--- a/engine/modon_study/MODON_Valuation_Model_09082026_public.xlsx
+++ b/engine/modon_study/MODON_Valuation_Model_09082026_public.xlsx
@@ -38,7 +38,7 @@
     <numFmt numFmtId="167" formatCode="0.00x"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,6 +78,10 @@
       <b val="1"/>
       <color rgb="00008000"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000000FF"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -114,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -148,12 +152,13 @@
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -519,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -536,7 +541,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Testahil — Modon Holding PSC (ADX: MODON)</t>
+          <t>Testahil — Modon Holding PSC (ADX: MODON) · Revision 2</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -561,318 +566,246 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>What this workbook is. A transparent companion to the MODON valuation study. Every blue cell is an input;</t>
+          <t>REVISION 2 (9 Aug 2026). This edition restrikes the valuation on the 30-Jun-2026 reviewed balance</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>every black cell is a formula; green cells link across sheets.</t>
+          <t>sheet and the H1-2026 results release (revenue backlog AED 65.4bn, 95% development; H1 real-estate</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr"/>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>sales AED 26bn) — disclosures the first edition failed to carry into its drivers, a defect surfaced</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>IT IS FORMULA-DRIVEN. Every figure that can be derived arithmetically from a driver is a live formula, so</t>
+          <t>by external audits and accepted. The audits' other accepted findings are implemented throughout:</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>you can change a blue cell on Assumptions and watch the model reprice: the cost of capital is built from</t>
+          <t>the bridge uses AVAILABLE cash (AED 8.6bn) rather than gross cash including project escrow; the</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>the AED government yield net of the sovereign spread, beta and the premium rather than pasted; the</t>
+          <t>terminal debt weight is DERIVED from the model's own terminal-year balance sheet; working capital</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>development backlog rolls forward in front of you (opening backlog + new sales − recognised revenue);</t>
+          <t>is built from components (receivable days, land-bank conversion, payables/advances cover); D&amp;A is</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>the DCF waterfall chains EBITDA → EBIT → NOPAT → free cash flow → present value; the terminal block</t>
+          <t>charged on the asset base; beta is a regression (1.03 vs an equal-weight panel proxy), no longer an</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>derives its reinvestment rate from growth over return on capital; and the income statement, balance</t>
+          <t>assumption; and the mid-chain hardcoded numerals the audits found are eliminated.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>sheet, cash flow, ratios and all four lenses chain off the same cells.</t>
-        </is>
-      </c>
+      <c r="A14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr"/>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>What this workbook is. Every blue cell is an input; every black cell is a formula; green cells link</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>THREE THINGS ARE PASTED VALUES, and it is worth knowing exactly which. First, audited and disclosed</t>
+          <t>across sheets. The cost of capital is built from the AED government yield net of the sovereign</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>history — the primary record, not a calculation (where a line is both disclosed and derivable, the</t>
+          <t>spread, beta and the premium; the development backlog rolls forward in front of you; the DCF</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>DISCLOSED figure is carried). Second, the FY2025 four-segment base — revenue, gross profit and assets</t>
+          <t>waterfall chains EBITDA → EBIT → NOPAT → free cash flow → present value; the terminal block derives</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>for the segments the company itself discloses (Real Estate Development; Asset &amp; Investment Management;</t>
+          <t>its reinvestment rate from growth over return on capital; the statements, ratios and all four</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Hospitality; Events, Catering &amp; Tourism) — pasted once, with the entire five-year forecast chaining off</t>
+          <t>lenses chain off the same cells.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>it as formulas. Third, whole-model engine outputs, where each figure is a complete re-run of the entire</t>
-        </is>
-      </c>
+      <c r="A21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>valuation and cannot be one formula: the Monte Carlo price map, the sensitivity grids, the DCF bear/bull</t>
+          <t>THREE THINGS ARE PASTED VALUES. First, audited and disclosed history (the primary record; where a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>scenario bounds (the backlog run-off and growth-hold alternatives) and the Egypt-risk stress. Those grids</t>
+          <t>line is both disclosed and derivable, the DISCLOSED figure is carried). Second, the FY2025</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>do NOT redraw when a driver changes; everything else reprices live.</t>
+          <t>four-segment base and the 30-Jun-2026 balance-sheet anchors — pasted once, with the entire forecast</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr"/>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>chaining off them as formulas. Third, whole-model engine outputs, where each figure is a complete</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>How revenue is built. Not as one growth rate. Development revenue converts the disclosed AED 42.6bn</t>
+          <t>re-run: the Monte Carlo price map, the sensitivity grids and the scenario outputs (run-off,</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>development backlog at a visible conversion rate, plus point-in-time land sales, with new launches</t>
+          <t>growth-hold, Egypt stress). Their DRIVER VECTORS are published on the Assumptions sheet so each</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>rolling the backlog forward on the sheet; the other three segments grow on their own drivers (occupancy</t>
+          <t>re-run is reproducible, but the grids do NOT redraw when a driver changes; everything else reprices</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>and GLA for asset management, keys × occupancy for hospitality, the events calendar for ECT). Margins</t>
+          <t>live, and the workbook forces a full recalculation when opened.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>are OUTPUTS of the segment build, not inputs to it.</t>
-        </is>
-      </c>
+      <c r="A30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr"/>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>The contested judgement, shown both ways. Base: the realised H1-2026 surge normalises but sustains.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>The contested judgement, shown both ways. Whether the record FY2025-26 development surge persists</t>
+          <t>Run-off (now labelled a stress — the H1 disclosure falsified it as a central path): launches halve</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>(base: normalising-but-sustained launches) or fades to backlog run-off is the single judgement that</t>
+          <t>and fade. Both DCFs are shown side by side; never averaged.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>moves this valuation most. Both DCFs are shown side by side on Fundamental Valuation and Summary;</t>
-        </is>
-      </c>
+      <c r="A34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>they are never averaged.</t>
+          <t>What it is not. Not investment advice, a recommendation, or a price target. Values are model</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr"/>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>outputs shown as ranges.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model</t>
-        </is>
-      </c>
+      <c r="A37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>outputs shown as ranges.</t>
+          <t>Currency. AED million unless stated. Spot AED 2.83 (7-Aug-2026 close); valuation date</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr"/>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>30-Jun-2026, rolled 38 days to the price anchor. Sheets: READ FIRST · Summary · Fundamental</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Sourcing note, up front. FY2023 (Q Holding perimeter), FY2024 and FY2025 all come from the company's own</t>
+          <t>Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income Statement ·</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>audited consolidated financial statements, retrieved from modon.com investor relations; H1-2026 from the</t>
+          <t>Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp; Ratios ·</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>reviewed interim. FY2024 is a perimeter break (the Modon Properties/ADNEC combination; bargain-purchase</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>gain AED 9,192mn) and is dual-framed wherever it appears. Every input is annotated where it appears and</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>listed with source and date in the companion bibliography document.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Discount convention. The explicit window discounts at a single AED cost of capital built on the sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>(the AED curve is flat-pegged to the USD; there is no easing glide to derive, and the discount factors</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>compound in front of you on the DCF sheet). The terminal value is capitalised at the terminal rate and</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>discounted at the year-5 factor. One date, one price of time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Currency. AED million unless stated. Spot AED 2.83 (2026-08-09 anchor; close 07-Aug-2026).</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Sheets: READ FIRST · Summary · Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp;</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Normalized · DCF · Income Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo ·</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Sensitivity · Per-Share &amp; Ratios · Peer &amp; Sector.</t>
+          <t>Peer &amp; Sector.</t>
         </is>
       </c>
     </row>
@@ -887,25 +820,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Balance sheet — 3 years audited + 5-year roll-forward</t>
+          <t>Balance sheet — audited history, 30-Jun-2026 actual, and the roll-forward</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -917,11 +851,12 @@
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Forecast: equity rolls on retained profit (no dividend); debt is the drawn path; cash balances derive</t>
+          <t>Column E = 30-Jun-2026 reviewed actuals; forecast rolls equity on retained profit, debt on the drawn path, cash from free cash flow</t>
         </is>
       </c>
     </row>
@@ -944,25 +879,30 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>FY26E</t>
+          <t>30-Jun-26A</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
+          <t>H2-26E</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
           <t>FY27E</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>FY28E</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>FY29E</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>FY30E</t>
         </is>
@@ -971,165 +911,167 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Property, plant &amp; equipment</t>
+          <t>Receivables incl. related-party</t>
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>789.463</v>
+        <v>1685.533</v>
       </c>
       <c r="C5" s="19" t="n">
-        <v>7593.191</v>
+        <v>12843.804</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>8812.397000000001</v>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>16635.123</v>
+      </c>
+      <c r="E5" s="18">
+        <f>Assumptions!$C$16</f>
+        <v/>
+      </c>
+      <c r="F5" s="18">
+        <f>DCF!B22</f>
+        <v/>
+      </c>
+      <c r="G5" s="18">
+        <f>DCF!C22</f>
+        <v/>
+      </c>
+      <c r="H5" s="18">
+        <f>DCF!D22</f>
+        <v/>
+      </c>
+      <c r="I5" s="18">
+        <f>DCF!E22</f>
+        <v/>
+      </c>
+      <c r="J5" s="18">
+        <f>DCF!F22</f>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Investment properties</t>
+          <t>Inventories + development WIP</t>
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>7536.858</v>
+        <v>2246.917</v>
       </c>
       <c r="C6" s="19" t="n">
-        <v>9336.725</v>
+        <v>32047.946</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>9461.777</v>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>33409.382</v>
+      </c>
+      <c r="E6" s="18">
+        <f>Assumptions!$C$17</f>
+        <v/>
+      </c>
+      <c r="F6" s="18">
+        <f>DCF!B23</f>
+        <v/>
+      </c>
+      <c r="G6" s="18">
+        <f>DCF!C23</f>
+        <v/>
+      </c>
+      <c r="H6" s="18">
+        <f>DCF!D23</f>
+        <v/>
+      </c>
+      <c r="I6" s="18">
+        <f>DCF!E23</f>
+        <v/>
+      </c>
+      <c r="J6" s="18">
+        <f>DCF!F23</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Inventories (land bank)</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="n">
-        <v>2246.917</v>
+          <t>Payables incl. advances + related-party</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C7" s="19" t="n">
-        <v>29586.274</v>
+        <v>18029.912</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>27297.588</v>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>23101.595</v>
+      </c>
+      <c r="E7" s="18">
+        <f>Assumptions!$C$18</f>
+        <v/>
+      </c>
+      <c r="F7" s="18">
+        <f>DCF!B24</f>
+        <v/>
+      </c>
+      <c r="G7" s="18">
+        <f>DCF!C24</f>
+        <v/>
+      </c>
+      <c r="H7" s="18">
+        <f>DCF!D24</f>
+        <v/>
+      </c>
+      <c r="I7" s="18">
+        <f>DCF!E24</f>
+        <v/>
+      </c>
+      <c r="J7" s="18">
+        <f>DCF!F24</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Development work-in-progress</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="19" t="n">
-        <v>2461.672</v>
-      </c>
-      <c r="D8" s="19" t="n">
-        <v>6111.794</v>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+          <t>Net working capital (components)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C8" s="17">
+        <f>C5+C6-C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="17">
+        <f>D5+D6-D7</f>
+        <v/>
+      </c>
+      <c r="E8" s="17">
+        <f>E5+E6-E7</f>
+        <v/>
+      </c>
+      <c r="F8" s="18">
+        <f>DCF!B25</f>
+        <v/>
+      </c>
+      <c r="G8" s="18">
+        <f>DCF!C25</f>
+        <v/>
+      </c>
+      <c r="H8" s="18">
+        <f>DCF!D25</f>
+        <v/>
+      </c>
+      <c r="I8" s="18">
+        <f>DCF!E25</f>
+        <v/>
+      </c>
+      <c r="J8" s="18">
+        <f>DCF!F25</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1147,24 +1089,28 @@
       <c r="D9" s="19" t="n">
         <v>12641.987</v>
       </c>
-      <c r="E9" s="17">
-        <f>D9+DCF!B18+'Income Statement'!E11-('Income Statement'!E13-DCF!B10)*Assumptions!$C$24+(Assumptions!$C$28-Assumptions!$C$43)</f>
+      <c r="E9" s="18">
+        <f>Assumptions!$C$9</f>
         <v/>
       </c>
       <c r="F9" s="17">
-        <f>E9+DCF!C18+'Income Statement'!F11-('Income Statement'!F13-DCF!C10)*Assumptions!$C$24+(Assumptions!$D$28-Assumptions!$C$28)</f>
+        <f>E9+DCF!B18+'Income Statement'!F11-('Income Statement'!F13-DCF!B10)*Assumptions!$C$48+(Assumptions!$C$51-Assumptions!$C$10)</f>
         <v/>
       </c>
       <c r="G9" s="17">
-        <f>F9+DCF!D18+'Income Statement'!G11-('Income Statement'!G13-DCF!D10)*Assumptions!$C$24+(Assumptions!$E$28-Assumptions!$D$28)</f>
+        <f>F9+DCF!C18+'Income Statement'!G11-('Income Statement'!G13-DCF!C10)*Assumptions!$C$48+(Assumptions!$D$51-Assumptions!$C$51)</f>
         <v/>
       </c>
       <c r="H9" s="17">
-        <f>G9+DCF!E18+'Income Statement'!H11-('Income Statement'!H13-DCF!E10)*Assumptions!$C$24+(Assumptions!$F$28-Assumptions!$E$28)</f>
+        <f>G9+DCF!D18+'Income Statement'!H11-('Income Statement'!H13-DCF!D10)*Assumptions!$C$48+(Assumptions!$E$51-Assumptions!$D$51)</f>
         <v/>
       </c>
       <c r="I9" s="17">
-        <f>H9+DCF!F18+'Income Statement'!I11-('Income Statement'!I13-DCF!F10)*Assumptions!$C$24+(Assumptions!$G$28-Assumptions!$F$28)</f>
+        <f>H9+DCF!E18+'Income Statement'!I11-('Income Statement'!I13-DCF!E10)*Assumptions!$C$48+(Assumptions!$F$51-Assumptions!$E$51)</f>
+        <v/>
+      </c>
+      <c r="J9" s="17">
+        <f>I9+DCF!F18+'Income Statement'!J11-('Income Statement'!J13-DCF!F10)*Assumptions!$C$48+(Assumptions!$G$51-Assumptions!$F$51)</f>
         <v/>
       </c>
     </row>
@@ -1183,214 +1129,198 @@
       <c r="D10" s="19" t="n">
         <v>87030.985</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="19" t="n">
+        <v>91985.92999999999</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Gross debt incl. related-party loan</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="n">
-        <v>1976.135</v>
-      </c>
-      <c r="C11" s="19" t="n">
-        <v>5364.11</v>
-      </c>
-      <c r="D11" s="19" t="n">
-        <v>6789.085999999999</v>
-      </c>
-      <c r="E11" s="18">
-        <f>Assumptions!$C$28</f>
-        <v/>
-      </c>
-      <c r="F11" s="18">
-        <f>Assumptions!$D$28</f>
-        <v/>
-      </c>
-      <c r="G11" s="18">
-        <f>Assumptions!$E$28</f>
-        <v/>
-      </c>
-      <c r="H11" s="18">
-        <f>Assumptions!$F$28</f>
-        <v/>
-      </c>
-      <c r="I11" s="18">
-        <f>Assumptions!$G$28</f>
-        <v/>
-      </c>
+      <c r="A11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Net working capital (house)</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Gross debt incl. related-party loan</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>1976.135</v>
       </c>
       <c r="C12" s="19" t="n">
-        <v>26861.838</v>
+        <v>5364.11</v>
       </c>
       <c r="D12" s="19" t="n">
-        <v>26942.91</v>
-      </c>
-      <c r="E12" s="17">
-        <f>26942.910-Assumptions!$C$23</f>
-        <v/>
-      </c>
-      <c r="F12" s="17">
-        <f>E12-Assumptions!$D$23</f>
-        <v/>
-      </c>
-      <c r="G12" s="17">
-        <f>F12-Assumptions!$E$23</f>
-        <v/>
-      </c>
-      <c r="H12" s="17">
-        <f>G12-Assumptions!$F$23</f>
-        <v/>
-      </c>
-      <c r="I12" s="17">
-        <f>H12-Assumptions!$G$23</f>
+        <v>6789.085999999999</v>
+      </c>
+      <c r="E12" s="18">
+        <f>Assumptions!$C$10</f>
+        <v/>
+      </c>
+      <c r="F12" s="18">
+        <f>Assumptions!$C$51</f>
+        <v/>
+      </c>
+      <c r="G12" s="18">
+        <f>Assumptions!$D$51</f>
+        <v/>
+      </c>
+      <c r="H12" s="18">
+        <f>Assumptions!$E$51</f>
+        <v/>
+      </c>
+      <c r="I12" s="18">
+        <f>Assumptions!$F$51</f>
+        <v/>
+      </c>
+      <c r="J12" s="18">
+        <f>Assumptions!$G$51</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Equity attributable to owners</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="n">
-        <v>13769.094</v>
-      </c>
-      <c r="C13" s="19" t="n">
-        <v>49676.408</v>
-      </c>
-      <c r="D13" s="19" t="n">
-        <v>53902.504</v>
+          <t>Net debt (− = net cash)</t>
+        </is>
+      </c>
+      <c r="B13" s="17">
+        <f>B12-B9</f>
+        <v/>
+      </c>
+      <c r="C13" s="17">
+        <f>C12-C9</f>
+        <v/>
+      </c>
+      <c r="D13" s="17">
+        <f>D12-D9</f>
+        <v/>
       </c>
       <c r="E13" s="17">
-        <f>D13+'Income Statement'!E17</f>
+        <f>E12-E9</f>
         <v/>
       </c>
       <c r="F13" s="17">
-        <f>E13+'Income Statement'!F17</f>
+        <f>F12-F9</f>
         <v/>
       </c>
       <c r="G13" s="17">
-        <f>F13+'Income Statement'!G17</f>
+        <f>G12-G9</f>
         <v/>
       </c>
       <c r="H13" s="17">
-        <f>G13+'Income Statement'!H17</f>
+        <f>H12-H9</f>
         <v/>
       </c>
       <c r="I13" s="17">
-        <f>H13+'Income Statement'!I17</f>
+        <f>I12-I9</f>
+        <v/>
+      </c>
+      <c r="J13" s="17">
+        <f>J12-J9</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Non-controlling interests</t>
+          <t>Equity attributable to owners</t>
         </is>
       </c>
       <c r="B14" s="19" t="n">
-        <v>1149.566</v>
+        <v>13769.094</v>
       </c>
       <c r="C14" s="19" t="n">
-        <v>1186.183</v>
+        <v>49676.408</v>
       </c>
       <c r="D14" s="19" t="n">
-        <v>847.48</v>
-      </c>
-      <c r="E14" s="17">
-        <f>D14+'Income Statement'!E16</f>
+        <v>53902.504</v>
+      </c>
+      <c r="E14" s="18">
+        <f>Assumptions!$C$15</f>
         <v/>
       </c>
       <c r="F14" s="17">
-        <f>E14+'Income Statement'!F16</f>
+        <f>E14+'Income Statement'!F17</f>
         <v/>
       </c>
       <c r="G14" s="17">
-        <f>F14+'Income Statement'!G16</f>
+        <f>F14+'Income Statement'!G17</f>
         <v/>
       </c>
       <c r="H14" s="17">
-        <f>G14+'Income Statement'!H16</f>
+        <f>G14+'Income Statement'!H17</f>
         <v/>
       </c>
       <c r="I14" s="17">
-        <f>H14+'Income Statement'!I16</f>
+        <f>H14+'Income Statement'!I17</f>
+        <v/>
+      </c>
+      <c r="J14" s="17">
+        <f>I14+'Income Statement'!J17</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Net debt (− = net cash)</t>
-        </is>
-      </c>
-      <c r="B15" s="17">
-        <f>B11-B9</f>
-        <v/>
-      </c>
-      <c r="C15" s="17">
-        <f>C11-C9</f>
-        <v/>
-      </c>
-      <c r="D15" s="17">
-        <f>D11-D9</f>
-        <v/>
-      </c>
-      <c r="E15" s="17">
-        <f>E11-E9</f>
+          <t>Non-controlling interests</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>1149.566</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>1186.183</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>847.48</v>
+      </c>
+      <c r="E15" s="18">
+        <f>Assumptions!$C$14</f>
         <v/>
       </c>
       <c r="F15" s="17">
-        <f>F11-F9</f>
+        <f>E15+'Income Statement'!F16</f>
         <v/>
       </c>
       <c r="G15" s="17">
-        <f>G11-G9</f>
+        <f>F15+'Income Statement'!G16</f>
         <v/>
       </c>
       <c r="H15" s="17">
-        <f>H11-H9</f>
+        <f>G15+'Income Statement'!H16</f>
         <v/>
       </c>
       <c r="I15" s="17">
-        <f>I11-I9</f>
+        <f>H15+'Income Statement'!I16</f>
+        <v/>
+      </c>
+      <c r="J15" s="17">
+        <f>I15+'Income Statement'!J16</f>
         <v/>
       </c>
     </row>
@@ -1401,35 +1331,35 @@
         </is>
       </c>
       <c r="B16" s="28">
-        <f>(B11-B9)/673.3530000000001</f>
+        <f>(B12-B9)/673.3530000000001</f>
         <v/>
       </c>
       <c r="C16" s="28">
-        <f>(C11-C9)/9794.942</f>
+        <f>(C12-C9)/9794.942</f>
         <v/>
       </c>
       <c r="D16" s="28">
-        <f>(D11-D9)/4895.552000000001</f>
-        <v/>
-      </c>
-      <c r="E16" s="28">
-        <f>(E11-E9)/DCF!B13</f>
+        <f>(D12-D9)/4895.552000000001</f>
         <v/>
       </c>
       <c r="F16" s="28">
-        <f>(F11-F9)/DCF!C13</f>
+        <f>(F12-F9)/DCF!B13</f>
         <v/>
       </c>
       <c r="G16" s="28">
-        <f>(G11-G9)/DCF!D13</f>
+        <f>(G12-G9)/DCF!C13</f>
         <v/>
       </c>
       <c r="H16" s="28">
-        <f>(H11-H9)/DCF!E13</f>
+        <f>(H12-H9)/DCF!D13</f>
         <v/>
       </c>
       <c r="I16" s="28">
-        <f>(I11-I9)/DCF!F13</f>
+        <f>(I12-I9)/DCF!E13</f>
+        <v/>
+      </c>
+      <c r="J16" s="28">
+        <f>(J12-J9)/DCF!F13</f>
         <v/>
       </c>
     </row>
@@ -1462,7 +1392,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cash flow — history (audited) and the forecast free-cash-flow chain</t>
+          <t>Cash flow — audited history, H1-2026 actual, and the forecast chain</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1478,7 +1408,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Forecast rows link to the DCF waterfall; history is the audited record</t>
+          <t>Forecast rows link to the DCF waterfall; the IFRS operating-cash-flow actuals are shown separately from the model construct (different measures, not one series)</t>
         </is>
       </c>
     </row>
@@ -1486,35 +1416,40 @@
       <c r="A4" s="5" t="inlineStr"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2024A</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2025A</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>FY26E</t>
+          <t>H1-26A</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>H2-26E</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>FY27E</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>FY28E</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>FY29E</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>FY30E</t>
         </is>
@@ -1523,7 +1458,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Net cash from operating activities (audited)</t>
+          <t>IFRS net cash from operating activities (audited/reviewed)</t>
         </is>
       </c>
       <c r="B5" s="19" t="n">
@@ -1532,11 +1467,14 @@
       <c r="C5" s="19" t="n">
         <v>3860.373</v>
       </c>
+      <c r="D5" s="19" t="n">
+        <v>-3921.027</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Capital expenditure (PP&amp;E + intangibles + IP, audited)</t>
+          <t>Capital expenditure (PP&amp;E + intangibles + IP)</t>
         </is>
       </c>
       <c r="B6" s="19" t="n">
@@ -1545,167 +1483,164 @@
       <c r="C6" s="19" t="n">
         <v>1260.566</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>H1-2026 operating cash flow (reviewed interim)</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="n">
-        <v>-3921.027</v>
+      <c r="D6" s="19" t="n">
+        <v>312.49</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Model construct (NOT the IFRS measure): links to the DCF waterfall</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
-        <is>
-          <t>Forecast chain (links to the DCF waterfall)</t>
-        </is>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>NOPAT</t>
+        </is>
+      </c>
+      <c r="E9" s="18">
+        <f>DCF!B14</f>
+        <v/>
+      </c>
+      <c r="F9" s="18">
+        <f>DCF!C14</f>
+        <v/>
+      </c>
+      <c r="G9" s="18">
+        <f>DCF!D14</f>
+        <v/>
+      </c>
+      <c r="H9" s="18">
+        <f>DCF!E14</f>
+        <v/>
+      </c>
+      <c r="I9" s="18">
+        <f>DCF!F14</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>NOPAT</t>
-        </is>
-      </c>
-      <c r="D10" s="18">
-        <f>DCF!B14</f>
-        <v/>
+          <t>+ D&amp;A</t>
+        </is>
       </c>
       <c r="E10" s="18">
-        <f>DCF!C14</f>
+        <f>DCF!B15</f>
         <v/>
       </c>
       <c r="F10" s="18">
-        <f>DCF!D14</f>
+        <f>DCF!C15</f>
         <v/>
       </c>
       <c r="G10" s="18">
-        <f>DCF!E14</f>
+        <f>DCF!D15</f>
         <v/>
       </c>
       <c r="H10" s="18">
-        <f>DCF!F14</f>
+        <f>DCF!E15</f>
+        <v/>
+      </c>
+      <c r="I10" s="18">
+        <f>DCF!F15</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>+ D&amp;A</t>
-        </is>
-      </c>
-      <c r="D11" s="18">
-        <f>DCF!B15</f>
-        <v/>
+          <t>− Capex</t>
+        </is>
       </c>
       <c r="E11" s="18">
-        <f>DCF!C15</f>
+        <f>DCF!B16</f>
         <v/>
       </c>
       <c r="F11" s="18">
-        <f>DCF!D15</f>
+        <f>DCF!C16</f>
         <v/>
       </c>
       <c r="G11" s="18">
-        <f>DCF!E15</f>
+        <f>DCF!D16</f>
         <v/>
       </c>
       <c r="H11" s="18">
-        <f>DCF!F15</f>
+        <f>DCF!E16</f>
+        <v/>
+      </c>
+      <c r="I11" s="18">
+        <f>DCF!F16</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>− Capex</t>
-        </is>
-      </c>
-      <c r="D12" s="18">
-        <f>DCF!B16</f>
-        <v/>
+          <t>− Δ working capital</t>
+        </is>
       </c>
       <c r="E12" s="18">
-        <f>DCF!C16</f>
+        <f>DCF!B17</f>
         <v/>
       </c>
       <c r="F12" s="18">
-        <f>DCF!D16</f>
+        <f>DCF!C17</f>
         <v/>
       </c>
       <c r="G12" s="18">
-        <f>DCF!E16</f>
+        <f>DCF!D17</f>
         <v/>
       </c>
       <c r="H12" s="18">
-        <f>DCF!F16</f>
+        <f>DCF!E17</f>
+        <v/>
+      </c>
+      <c r="I12" s="18">
+        <f>DCF!F17</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>− Δ working capital</t>
-        </is>
-      </c>
-      <c r="D13" s="18">
-        <f>DCF!B17</f>
-        <v/>
-      </c>
-      <c r="E13" s="18">
-        <f>DCF!C17</f>
-        <v/>
-      </c>
-      <c r="F13" s="18">
-        <f>DCF!D17</f>
-        <v/>
-      </c>
-      <c r="G13" s="18">
-        <f>DCF!E17</f>
-        <v/>
-      </c>
-      <c r="H13" s="18">
-        <f>DCF!F17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
           <t>Free cash flow to firm</t>
         </is>
       </c>
-      <c r="D14" s="33">
+      <c r="E13" s="34">
         <f>DCF!B18</f>
         <v/>
       </c>
-      <c r="E14" s="33">
+      <c r="F13" s="34">
         <f>DCF!C18</f>
         <v/>
       </c>
-      <c r="F14" s="33">
+      <c r="G13" s="34">
         <f>DCF!D18</f>
         <v/>
       </c>
-      <c r="G14" s="33">
+      <c r="H13" s="34">
         <f>DCF!E18</f>
         <v/>
       </c>
-      <c r="H14" s="33">
+      <c r="I13" s="34">
         <f>DCF!F18</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Forecast years run FY2026E..FY2030E in columns D..H</t>
-        </is>
-      </c>
-    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>Implied H2-2026 IFRS-basis operating recovery required by the model: the H1 actual was −3,921; the model's FY2026 working-capital absorption of 938 implies roughly +5,978 of H2 operating cash flow — stated, not hidden</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A15:I16"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1716,19 +1651,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1746,6 +1682,7 @@
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -1773,25 +1710,30 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>FY26E</t>
+          <t>H1-26A</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
+          <t>H2-26E</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
           <t>FY27E</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>FY28E</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>FY29E</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>FY30E</t>
         </is>
@@ -1835,6 +1777,10 @@
         <f>'Income Statement'!I5</f>
         <v/>
       </c>
+      <c r="J5" s="18">
+        <f>'Income Statement'!J5</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1854,9 +1800,10 @@
         <f>'Income Statement'!D7</f>
         <v/>
       </c>
-      <c r="E6" s="18">
-        <f>'Income Statement'!E7</f>
-        <v/>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F6" s="18">
         <f>'Income Statement'!F7</f>
@@ -1874,6 +1821,10 @@
         <f>'Income Statement'!I7</f>
         <v/>
       </c>
+      <c r="J6" s="18">
+        <f>'Income Statement'!J7</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -1893,9 +1844,10 @@
         <f>'Income Statement'!D8</f>
         <v/>
       </c>
-      <c r="E7" s="9">
-        <f>'Income Statement'!E8</f>
-        <v/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F7" s="9">
         <f>'Income Statement'!F8</f>
@@ -1913,6 +1865,10 @@
         <f>'Income Statement'!I8</f>
         <v/>
       </c>
+      <c r="J7" s="9">
+        <f>'Income Statement'!J8</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1952,6 +1908,10 @@
         <f>'Income Statement'!I17</f>
         <v/>
       </c>
+      <c r="J8" s="18">
+        <f>'Income Statement'!J17</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1974,24 +1934,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E9" s="18">
-        <f>'Cash Flow'!D14</f>
-        <v/>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F9" s="18">
-        <f>'Cash Flow'!E14</f>
+        <f>'Cash Flow'!E13</f>
         <v/>
       </c>
       <c r="G9" s="18">
-        <f>'Cash Flow'!F14</f>
+        <f>'Cash Flow'!F13</f>
         <v/>
       </c>
       <c r="H9" s="18">
-        <f>'Cash Flow'!G14</f>
+        <f>'Cash Flow'!G13</f>
         <v/>
       </c>
       <c r="I9" s="18">
-        <f>'Cash Flow'!H14</f>
+        <f>'Cash Flow'!H13</f>
+        <v/>
+      </c>
+      <c r="J9" s="18">
+        <f>'Cash Flow'!I13</f>
         <v/>
       </c>
     </row>
@@ -2002,35 +1967,39 @@
         </is>
       </c>
       <c r="B10" s="18">
-        <f>'Balance Sheet'!B15</f>
+        <f>'Balance Sheet'!B13</f>
         <v/>
       </c>
       <c r="C10" s="18">
-        <f>'Balance Sheet'!C15</f>
+        <f>'Balance Sheet'!C13</f>
         <v/>
       </c>
       <c r="D10" s="18">
-        <f>'Balance Sheet'!D15</f>
+        <f>'Balance Sheet'!D13</f>
         <v/>
       </c>
       <c r="E10" s="18">
-        <f>'Balance Sheet'!E15</f>
+        <f>'Balance Sheet'!E13</f>
         <v/>
       </c>
       <c r="F10" s="18">
-        <f>'Balance Sheet'!F15</f>
+        <f>'Balance Sheet'!F13</f>
         <v/>
       </c>
       <c r="G10" s="18">
-        <f>'Balance Sheet'!G15</f>
+        <f>'Balance Sheet'!G13</f>
         <v/>
       </c>
       <c r="H10" s="18">
-        <f>'Balance Sheet'!H15</f>
+        <f>'Balance Sheet'!H13</f>
         <v/>
       </c>
       <c r="I10" s="18">
-        <f>'Balance Sheet'!I15</f>
+        <f>'Balance Sheet'!I13</f>
+        <v/>
+      </c>
+      <c r="J10" s="18">
+        <f>'Balance Sheet'!J13</f>
         <v/>
       </c>
     </row>
@@ -2041,62 +2010,73 @@
         </is>
       </c>
       <c r="B11" s="18">
-        <f>'Balance Sheet'!B13</f>
+        <f>'Balance Sheet'!B14</f>
         <v/>
       </c>
       <c r="C11" s="18">
-        <f>'Balance Sheet'!C13</f>
+        <f>'Balance Sheet'!C14</f>
         <v/>
       </c>
       <c r="D11" s="18">
-        <f>'Balance Sheet'!D13</f>
+        <f>'Balance Sheet'!D14</f>
         <v/>
       </c>
       <c r="E11" s="18">
-        <f>'Balance Sheet'!E13</f>
+        <f>'Balance Sheet'!E14</f>
         <v/>
       </c>
       <c r="F11" s="18">
-        <f>'Balance Sheet'!F13</f>
+        <f>'Balance Sheet'!F14</f>
         <v/>
       </c>
       <c r="G11" s="18">
-        <f>'Balance Sheet'!G13</f>
+        <f>'Balance Sheet'!G14</f>
         <v/>
       </c>
       <c r="H11" s="18">
-        <f>'Balance Sheet'!H13</f>
+        <f>'Balance Sheet'!H14</f>
         <v/>
       </c>
       <c r="I11" s="18">
-        <f>'Balance Sheet'!I13</f>
-        <v/>
-      </c>
+        <f>'Balance Sheet'!I14</f>
+        <v/>
+      </c>
+      <c r="J11" s="18">
+        <f>'Balance Sheet'!J14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Invested capital (FY2025 base + cumulative capex − D&amp;A + ΔWC)</t>
+          <t>Invested capital: 30-Jun-2026 base + cumulative (capex − D&amp;A + ΔWC)</t>
         </is>
       </c>
       <c r="E13" s="17">
-        <f>48897.083+DCF!B16*-1-DCF!B12-DCF!B17</f>
+        <f>Assumptions!$C$15+Assumptions!$C$14+Assumptions!$C$10-Assumptions!$C$9</f>
         <v/>
       </c>
       <c r="F13" s="17">
-        <f>48897.083+DCF!B16*-1-DCF!B12-DCF!B17+DCF!C16*-1-DCF!C12-DCF!C17</f>
+        <f>E13+DCF!B16*-1-DCF!B12+DCF!B26</f>
         <v/>
       </c>
       <c r="G13" s="17">
-        <f>48897.083+DCF!B16*-1-DCF!B12-DCF!B17+DCF!C16*-1-DCF!C12-DCF!C17+DCF!D16*-1-DCF!D12-DCF!D17</f>
+        <f>F13+DCF!C16*-1-DCF!C12+DCF!C26</f>
         <v/>
       </c>
       <c r="H13" s="17">
-        <f>48897.083+DCF!B16*-1-DCF!B12-DCF!B17+DCF!C16*-1-DCF!C12-DCF!C17+DCF!D16*-1-DCF!D12-DCF!D17+DCF!E16*-1-DCF!E12-DCF!E17</f>
+        <f>G13+DCF!D16*-1-DCF!D12+DCF!D26</f>
         <v/>
       </c>
       <c r="I13" s="17">
-        <f>48897.083+DCF!B16*-1-DCF!B12-DCF!B17+DCF!C16*-1-DCF!C12-DCF!C17+DCF!D16*-1-DCF!D12-DCF!D17+DCF!E16*-1-DCF!E12-DCF!E17+DCF!F16*-1-DCF!F12-DCF!F17</f>
+        <f>H13+DCF!E16*-1-DCF!E12+DCF!E26</f>
+        <v/>
+      </c>
+      <c r="J13" s="17">
+        <f>I13+DCF!F16*-1-DCF!F12+DCF!F26</f>
         <v/>
       </c>
     </row>
@@ -2139,7 +2119,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Struck 2026-08-07 at spot 2.83; 50,000 paths, seed 42; grade dates are calendar-resolved</t>
+          <t>Struck 2026-08-07 at spot 2.83; 50,000 paths, seed 42; unchanged from the first edition (the price series and anchor are unchanged)</t>
         </is>
       </c>
     </row>
@@ -2175,12 +2155,12 @@
           <t>Grade date</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
@@ -2362,7 +2342,7 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="B22" s="34" t="inlineStr">
+      <c r="B22" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2371,7 +2351,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Coverage of the 80% band</t>
+          <t>Coverage of the 80% band (over-covered: bands run wide)</t>
         </is>
       </c>
       <c r="B23" s="24" t="n">
@@ -2394,7 +2374,7 @@
           <t>PIT mean (0.5 = centred)</t>
         </is>
       </c>
-      <c r="B25" s="35" t="n">
+      <c r="B25" s="37" t="n">
         <v>0.439185294117647</v>
       </c>
     </row>
@@ -2409,7 +2389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2437,14 +2417,14 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Rows: cost of capital; columns: terminal growth. Additional one-way strips below</t>
+          <t>Rebuilt at revision 2 on the base convention: explicit and terminal rates shift TOGETHER, so the centre cell equals the base case. Driver vectors on Assumptions</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>WACC \ g</t>
+          <t>Ke shift \ g</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -2476,142 +2456,142 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>7.37%</t>
+          <t>7.30%</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>6.816452482925069</v>
+        <v>6.042201126082581</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>6.909873380799658</v>
+        <v>6.10721428904692</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>7.018543394391232</v>
+        <v>6.180544547870568</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>7.147700584854253</v>
+        <v>6.264795543624948</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>7.305292247434371</v>
+        <v>6.363784279482363</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>7.87%</t>
+          <t>7.80%</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>6.327851843498262</v>
+        <v>5.630966604933419</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>6.380928636790108</v>
+        <v>5.664779705951927</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>6.44039871910471</v>
+        <v>5.700881174225827</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>6.50823256238644</v>
+        <v>5.739924640865718</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>6.587303112991017</v>
+        <v>5.782838862569954</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>8.37%</t>
+          <t>8.30%</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>5.909838209003201</v>
+        <v>5.272022262605483</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>5.934227354209989</v>
+        <v>5.28268685237433</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>5.959648219937487</v>
+        <v>5.291798921725333</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>5.986389167001941</v>
+        <v>5.298950728670187</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>6.014857056915395</v>
+        <v>5.303578050656447</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>8.87%</t>
+          <t>8.80%</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>5.548060984956186</v>
+        <v>4.95597119576637</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>5.551834193925449</v>
+        <v>4.94933727846957</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>5.55338560371135</v>
+        <v>4.938715350961064</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5.55214715556825</v>
+        <v>4.923136085639504</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>5.547339097912793</v>
+        <v>4.90128831902279</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>9.37%</t>
+          <t>9.30%</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>5.231817129849231</v>
+        <v>4.675542181427662</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>5.220681935737598</v>
+        <v>4.655928128818662</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>5.205374749702586</v>
+        <v>4.630809313035305</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>5.184912665481165</v>
+        <v>4.598940538029852</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>5.157977703923985</v>
+        <v>4.558670424322702</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Beta</t>
+          <t>Beta 0.8 → 1.2 (base 1.03)</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.20</t>
         </is>
       </c>
     </row>
@@ -2622,25 +2602,25 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>6.866679344218397</v>
+        <v>6.308360959810829</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>6.413169493505883</v>
+        <v>5.820961579529833</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>6.024236149749804</v>
+        <v>5.291798921725333</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>5.686927547554161</v>
+        <v>5.045711292286136</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>5.391541877257699</v>
+        <v>4.732247716753633</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Development margin shift</t>
+          <t>Development margin shift (pts)</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -2655,17 +2635,17 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>+0.00</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>+0.02</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>+0.04</t>
         </is>
       </c>
     </row>
@@ -2676,25 +2656,25 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>5.43240572430237</v>
+        <v>4.792998926154786</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>5.728320937026088</v>
+        <v>5.042398923940059</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.024236149749804</v>
+        <v>5.291798921725333</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>6.320151362473521</v>
+        <v>5.541198919510606</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>6.616066575197236</v>
+        <v>5.790598917295879</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Conversion-rate shift</t>
+          <t>Conversion-rate shift (pts)</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -2709,17 +2689,17 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>+0.00</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>+0.03</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>+0.06</t>
         </is>
       </c>
     </row>
@@ -2730,30 +2710,30 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>5.68305748265587</v>
+        <v>4.849341985216689</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>5.869617894273379</v>
+        <v>5.088978093938395</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>6.024236149749804</v>
+        <v>5.291798921725333</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>6.151121771303977</v>
+        <v>5.462012652655713</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>6.254107573264127</v>
+        <v>5.603513696301147</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>New-sales multiple</t>
+          <t>New-sales multiple of base</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -2763,7 +2743,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2773,7 +2753,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.50</t>
         </is>
       </c>
     </row>
@@ -2784,50 +2764,50 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>4.467805933968548</v>
+        <v>4.098077467988583</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>5.246021041859176</v>
+        <v>4.694938194856958</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>6.024236149749804</v>
+        <v>5.291798921725333</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>6.80245125764043</v>
+        <v>5.888659648593707</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>7.580666365531059</v>
+        <v>6.485520375462085</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Working-capital release shift (AED mn/yr)</t>
+          <t>Working-capital shift (AED mn/yr)</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>-1000.0</t>
+          <t>-1000</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>-500.0</t>
+          <t>-500</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>+0</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>+500</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>+1000</t>
         </is>
       </c>
     </row>
@@ -2838,50 +2818,50 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>5.76959452732698</v>
+        <v>5.042406761281446</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>5.896915338538393</v>
+        <v>5.167102841503389</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>6.024236149749804</v>
+        <v>5.291798921725333</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>6.151556960961216</v>
+        <v>5.416495001947276</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>6.278877772172628</v>
+        <v>5.541191082169219</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Cost-of-equity adder</t>
+          <t>Receivable-days shift</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-60</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-30</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>+0</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>+30</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>+60</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2872,73 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>6.024236149749804</v>
+        <v>5.615709443012417</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>5.678535191814055</v>
+        <v>5.453754182368876</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>5.376799558560899</v>
+        <v>5.291798921725333</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>5.111087154173134</v>
+        <v>5.12984366108179</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>4.875262927275586</v>
+        <v>4.967888400438247</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Cost-of-equity adder (0 = base)</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>+0.000</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+0.005</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>+0.010</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>+0.015</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>+0.020</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>DCF per share</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>5.291798921725333</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>4.938715350961064</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>4.630809313035305</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>4.359881599769382</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>4.119606091590888</v>
       </c>
     </row>
   </sheetData>
@@ -2918,25 +2952,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Per-share figures and ratios — all formulas</t>
+          <t>Per-share figures and ratios — all live formulas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2948,6 +2983,7 @@
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr"/>
@@ -2968,25 +3004,30 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>FY26E</t>
+          <t>H1-26A</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
+          <t>H2-26E</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
           <t>FY27E</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>FY28E</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>FY29E</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>FY30E</t>
         </is>
@@ -2995,7 +3036,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>EPS (attributable)</t>
+          <t>EPS (attributable; H1 and the stub are part-year)</t>
         </is>
       </c>
       <c r="B5" s="8">
@@ -3030,6 +3071,10 @@
         <f>'Income Statement'!I17/Assumptions!$C$5</f>
         <v/>
       </c>
+      <c r="J5" s="8">
+        <f>'Income Statement'!J17/Assumptions!$C$5</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -3038,42 +3083,46 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>'Balance Sheet'!B13/Assumptions!$C$5</f>
+        <f>'Balance Sheet'!B14/Assumptions!$C$5</f>
         <v/>
       </c>
       <c r="C6" s="8">
-        <f>'Balance Sheet'!C13/Assumptions!$C$5</f>
+        <f>'Balance Sheet'!C14/Assumptions!$C$5</f>
         <v/>
       </c>
       <c r="D6" s="8">
-        <f>'Balance Sheet'!D13/Assumptions!$C$5</f>
+        <f>'Balance Sheet'!D14/Assumptions!$C$5</f>
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>'Balance Sheet'!E13/Assumptions!$C$5</f>
+        <f>'Balance Sheet'!E14/Assumptions!$C$5</f>
         <v/>
       </c>
       <c r="F6" s="8">
-        <f>'Balance Sheet'!F13/Assumptions!$C$5</f>
+        <f>'Balance Sheet'!F14/Assumptions!$C$5</f>
         <v/>
       </c>
       <c r="G6" s="8">
-        <f>'Balance Sheet'!G13/Assumptions!$C$5</f>
+        <f>'Balance Sheet'!G14/Assumptions!$C$5</f>
         <v/>
       </c>
       <c r="H6" s="8">
-        <f>'Balance Sheet'!H13/Assumptions!$C$5</f>
+        <f>'Balance Sheet'!H14/Assumptions!$C$5</f>
         <v/>
       </c>
       <c r="I6" s="8">
-        <f>'Balance Sheet'!I13/Assumptions!$C$5</f>
+        <f>'Balance Sheet'!I14/Assumptions!$C$5</f>
+        <v/>
+      </c>
+      <c r="J6" s="8">
+        <f>'Balance Sheet'!J14/Assumptions!$C$5</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Return on attributable equity (avg)</t>
+          <t>Return on attributable equity (avg; part-year annualised)</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -3082,38 +3131,42 @@
         </is>
       </c>
       <c r="C7" s="9">
-        <f>'Income Statement'!C17/(('Balance Sheet'!C13+'Balance Sheet'!B13)/2)</f>
+        <f>'Income Statement'!C17/1.0/(('Balance Sheet'!C14+'Balance Sheet'!B14)/2)</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>'Income Statement'!D17/(('Balance Sheet'!D13+'Balance Sheet'!C13)/2)</f>
+        <f>'Income Statement'!D17/1.0/(('Balance Sheet'!D14+'Balance Sheet'!C14)/2)</f>
         <v/>
       </c>
       <c r="E7" s="9">
-        <f>'Income Statement'!E17/(('Balance Sheet'!E13+'Balance Sheet'!D13)/2)</f>
+        <f>'Income Statement'!E17/0.5/(('Balance Sheet'!E14+'Balance Sheet'!D14)/2)</f>
         <v/>
       </c>
       <c r="F7" s="9">
-        <f>'Income Statement'!F17/(('Balance Sheet'!F13+'Balance Sheet'!E13)/2)</f>
+        <f>'Income Statement'!F17/0.5/(('Balance Sheet'!F14+'Balance Sheet'!E14)/2)</f>
         <v/>
       </c>
       <c r="G7" s="9">
-        <f>'Income Statement'!G17/(('Balance Sheet'!G13+'Balance Sheet'!F13)/2)</f>
+        <f>'Income Statement'!G17/1.0/(('Balance Sheet'!G14+'Balance Sheet'!F14)/2)</f>
         <v/>
       </c>
       <c r="H7" s="9">
-        <f>'Income Statement'!H17/(('Balance Sheet'!H13+'Balance Sheet'!G13)/2)</f>
+        <f>'Income Statement'!H17/1.0/(('Balance Sheet'!H14+'Balance Sheet'!G14)/2)</f>
         <v/>
       </c>
       <c r="I7" s="9">
-        <f>'Income Statement'!I17/(('Balance Sheet'!I13+'Balance Sheet'!H13)/2)</f>
+        <f>'Income Statement'!I17/1.0/(('Balance Sheet'!I14+'Balance Sheet'!H14)/2)</f>
+        <v/>
+      </c>
+      <c r="J7" s="9">
+        <f>'Income Statement'!J17/1.0/(('Balance Sheet'!J14+'Balance Sheet'!I14)/2)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Return on invested capital (fwd, avg base)</t>
+          <t>Return on invested capital (avg base, annualised)</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -3131,26 +3184,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E8" s="24" t="n">
-        <v>0.08647173741449364</v>
-      </c>
-      <c r="F8" s="24" t="n">
-        <v>0.1111631649217001</v>
-      </c>
-      <c r="G8" s="24" t="n">
-        <v>0.1288010053835826</v>
-      </c>
-      <c r="H8" s="24" t="n">
-        <v>0.141920554298667</v>
-      </c>
-      <c r="I8" s="24" t="n">
-        <v>0.1502532912420733</v>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="9">
+        <f>DCF!B14/0.5/(('Summary Financials'!F13+'Summary Financials'!E13)/2)</f>
+        <v/>
+      </c>
+      <c r="G8" s="9">
+        <f>DCF!C14/1.0/(('Summary Financials'!G13+'Summary Financials'!F13)/2)</f>
+        <v/>
+      </c>
+      <c r="H8" s="9">
+        <f>DCF!D14/1.0/(('Summary Financials'!H13+'Summary Financials'!G13)/2)</f>
+        <v/>
+      </c>
+      <c r="I8" s="9">
+        <f>DCF!E14/1.0/(('Summary Financials'!I13+'Summary Financials'!H13)/2)</f>
+        <v/>
+      </c>
+      <c r="J8" s="9">
+        <f>DCF!F14/1.0/(('Summary Financials'!J13+'Summary Financials'!I13)/2)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>P/E at spot</t>
+          <t>P/E at spot (full years)</t>
         </is>
       </c>
       <c r="B9" s="28">
@@ -3165,13 +3228,15 @@
         <f>Assumptions!$C$4/D5</f>
         <v/>
       </c>
-      <c r="E9" s="28">
-        <f>Assumptions!$C$4/E5</f>
-        <v/>
-      </c>
-      <c r="F9" s="28">
-        <f>Assumptions!$C$4/F5</f>
-        <v/>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G9" s="28">
         <f>Assumptions!$C$4/G5</f>
@@ -3185,6 +3250,10 @@
         <f>Assumptions!$C$4/I5</f>
         <v/>
       </c>
+      <c r="J9" s="28">
+        <f>Assumptions!$C$4/J5</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -3222,6 +3291,10 @@
       </c>
       <c r="I10" s="28">
         <f>Assumptions!$C$4/I6</f>
+        <v/>
+      </c>
+      <c r="J10" s="28">
+        <f>Assumptions!$C$4/J6</f>
         <v/>
       </c>
     </row>
@@ -3236,23 +3309,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peer &amp; sector — cross-checks only, never build sources</t>
+          <t>Peer &amp; sector — one attributable basis, cross-checks only</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3266,7 +3339,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Peer fundamentals from each company's own FY2025 release; prices/multiples from stockanalysis.com 07-Aug-2026 (aggregator, labelled)</t>
+          <t>Peer attributable profits from each company's own audited filings/releases; prices 7-Aug-2026; every multiple is a live formula from its own row</t>
         </is>
       </c>
     </row>
@@ -3283,27 +3356,27 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Mkt cap (AED mn)</t>
+          <t>Shares (mn)</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>FY2025 NP (AED mn)</t>
+          <t>Mkt cap</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Trailing P/E</t>
+          <t>FY2025 attributable NP</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>FY2025 revenue</t>
+          <t>Trailing P/E (attr)</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Backlog (own disclosure)</t>
         </is>
       </c>
     </row>
@@ -3317,19 +3390,21 @@
         <v>7.78</v>
       </c>
       <c r="C5" s="19" t="n">
-        <v>61170</v>
-      </c>
-      <c r="D5" s="19" t="n">
-        <v>8800</v>
-      </c>
-      <c r="E5" s="25" t="n">
-        <v>7.54</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>33800</v>
+        <v>7862.6</v>
+      </c>
+      <c r="D5" s="17">
+        <f>B5*C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>7548</v>
+      </c>
+      <c r="F5" s="28">
+        <f>D5/E5</f>
+        <v/>
       </c>
       <c r="G5" s="19" t="n">
-        <v>66500</v>
+        <v>71700</v>
       </c>
     </row>
     <row r="6">
@@ -3342,18 +3417,18 @@
         <v>11.5</v>
       </c>
       <c r="C6" s="19" t="n">
-        <v>101650</v>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="25" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>49600</v>
+        <v>8838</v>
+      </c>
+      <c r="D6" s="17">
+        <f>B6*C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>17599</v>
+      </c>
+      <c r="F6" s="28">
+        <f>D6/E6</f>
+        <v/>
       </c>
       <c r="G6" s="19" t="n">
         <v>155000</v>
@@ -3369,19 +3444,21 @@
         <v>13.38</v>
       </c>
       <c r="C7" s="19" t="n">
-        <v>53520</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>11320</v>
-      </c>
-      <c r="E7" s="25" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>27490</v>
+        <v>4000</v>
+      </c>
+      <c r="D7" s="17">
+        <f>B7*C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>11316</v>
+      </c>
+      <c r="F7" s="28">
+        <f>D7/E7</f>
+        <v/>
       </c>
       <c r="G7" s="19" t="n">
-        <v>134300</v>
+        <v>125200</v>
       </c>
     </row>
     <row r="8">
@@ -3394,37 +3471,45 @@
         <f>Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="C8" s="17">
-        <f>Assumptions!$C$4*Assumptions!$C$5</f>
-        <v/>
-      </c>
-      <c r="D8" s="19" t="n">
-        <v>3925.705</v>
-      </c>
-      <c r="E8" s="28">
-        <f>C8/D8</f>
-        <v/>
-      </c>
-      <c r="F8" s="18">
-        <f>'Income Statement'!D5</f>
+      <c r="C8" s="18">
+        <f>Assumptions!$C$5</f>
+        <v/>
+      </c>
+      <c r="D8" s="17">
+        <f>B8*C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="18">
+        <f>Assumptions!$C$71</f>
+        <v/>
+      </c>
+      <c r="F8" s="28">
+        <f>D8/E8</f>
         <v/>
       </c>
       <c r="G8" s="19" t="n">
-        <v>46000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="36" t="inlineStr">
-        <is>
-          <t>Sector context (ADREC 2025, regulator): AED 142bn transactions (+44%); residential AED 76bn (+67%); off-plan 71% of residential deals; foreign buyers 62% of growth.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+        <v>65400</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (Modon backlog = 30-Jun-2026 group figure; peers = FY2025 development backlogs from their own releases — one definition per row, dated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>Sector context (ADREC 2025, regulator): AED 142bn transactions (+44%); residential AED 76bn (+67%); off-plan 71% of residential deals; expatriate and foreign buyers 62% of residential sales value.</t>
+        </is>
+      </c>
+    </row>
     <row r="12"/>
+    <row r="13"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:G12"/>
+    <mergeCell ref="A11:G13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3436,7 +3521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3451,7 +3536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Summary — valuation at a glance</t>
+          <t>Summary — valuation at a glance (revision 2)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3512,17 +3597,17 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>4.179391161327742</v>
+        <v>3.784078327184524</v>
       </c>
       <c r="C5" s="8">
-        <f>DCF!C54</f>
+        <f>DCF!C62</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>7.393430194946205</v>
+        <v>6.305618176058718</v>
       </c>
       <c r="E5" s="9">
-        <f>Assumptions!$C$57</f>
+        <f>Assumptions!$C$82</f>
         <v/>
       </c>
       <c r="F5" s="10">
@@ -3553,7 +3638,7 @@
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>Assumptions!$C$58</f>
+        <f>Assumptions!$C$83</f>
         <v/>
       </c>
       <c r="F6" s="10">
@@ -3584,7 +3669,7 @@
         <v/>
       </c>
       <c r="E7" s="9">
-        <f>Assumptions!$C$59</f>
+        <f>Assumptions!$C$84</f>
         <v/>
       </c>
       <c r="F7" s="10">
@@ -3615,7 +3700,7 @@
         <v/>
       </c>
       <c r="E8" s="9">
-        <f>Assumptions!$C$60</f>
+        <f>Assumptions!$C$85</f>
         <v/>
       </c>
       <c r="F8" s="10">
@@ -3658,15 +3743,15 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>The contested judgement, both ways: DCF base vs backlog run-off</t>
+          <t>The contested judgement: DCF base vs run-off stress</t>
         </is>
       </c>
       <c r="C11" s="8">
-        <f>DCF!C54</f>
+        <f>DCF!C62</f>
         <v/>
       </c>
       <c r="D11" s="7" t="n">
-        <v>4.179391161327742</v>
+        <v>3.784078327184524</v>
       </c>
     </row>
     <row r="12">
@@ -3676,7 +3761,7 @@
         </is>
       </c>
       <c r="C12" s="9">
-        <f>DCF!C42</f>
+        <f>DCF!C49</f>
         <v/>
       </c>
     </row>
@@ -3687,7 +3772,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>3.923210931248883</v>
+        <v>3.619591626807453</v>
       </c>
     </row>
     <row r="14">
@@ -3732,169 +3817,158 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Net cash, strict basis (cash − debt, FY2025)</t>
+          <t>Net cash, strict basis (all cash − all debt, 30-Jun-2026)</t>
         </is>
       </c>
       <c r="C18" s="18">
-        <f>Assumptions!$C$42-Assumptions!$C$43</f>
+        <f>Assumptions!$C$9-Assumptions!$C$10</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Net cash, company definition (disclosed)</t>
+          <t>Net debt, company definition (available cash − debt, disclosed)</t>
         </is>
       </c>
       <c r="C19" s="19" t="n">
-        <v>1800</v>
+        <v>-912</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>FY2025 revenue (AED mn)</t>
+          <t>FY2026E revenue (H1 actual + H2 model)</t>
         </is>
       </c>
       <c r="C20" s="18">
-        <f>'Income Statement'!D5</f>
+        <f>Assumptions!$C$19+DCF!B5</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>FY2025 EBITDA (AED mn)</t>
+          <t>FY2026E attributable profit</t>
         </is>
       </c>
       <c r="C21" s="18">
-        <f>'Income Statement'!D7</f>
+        <f>'Relative &amp; Normalized'!C5</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>FY2025 attributable profit (AED mn)</t>
-        </is>
-      </c>
-      <c r="C22" s="18">
-        <f>'Income Statement'!D17</f>
+          <t>Cost of capital (explicit window)</t>
+        </is>
+      </c>
+      <c r="C22" s="20">
+        <f>DCF!C36</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Cost of capital (explicit window)</t>
+          <t>Cost of capital (terminal, derived weights)</t>
         </is>
       </c>
       <c r="C23" s="20">
-        <f>DCF!C30</f>
+        <f>DCF!C38</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Cost of capital (terminal)</t>
+          <t>Terminal growth</t>
         </is>
       </c>
       <c r="C24" s="20">
-        <f>DCF!C31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="C25" s="20">
-        <f>Assumptions!$C$38</f>
-        <v/>
+        <f>Assumptions!$C$66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Monte Carlo price map (engine re-run, pasted)</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>1 month</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Monte Carlo price map (engine re-run, pasted)</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>1 month</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>3 months</t>
-        </is>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>5th percentile</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>2.537067974301798</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>2.319965747344324</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>5th percentile</t>
+          <t>25th percentile</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>2.537067974301798</v>
+        <v>2.718595960543321</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>2.319965747344324</v>
+        <v>2.637975726186433</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>25th percentile</t>
+          <t>Median</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>2.718595960543321</v>
+        <v>2.838308856303401</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>2.637975726186433</v>
+        <v>2.857647930306376</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Median</t>
+          <t>75th percentile</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>2.838308856303401</v>
+        <v>2.963942198127806</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>2.857647930306376</v>
+        <v>3.094773382373537</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>75th percentile</t>
+          <t>95th percentile</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>2.963942198127806</v>
+        <v>3.169632883184554</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>3.094773382373537</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>95th percentile</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="n">
-        <v>3.169632883184554</v>
-      </c>
-      <c r="C32" s="7" t="n">
         <v>3.523723381103312</v>
       </c>
     </row>
@@ -3909,7 +3983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -3923,7 +3997,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Fundamental valuation — four lenses, the contested judgement and the stress readings</t>
+          <t>Fundamental valuation — four lenses, the contested judgement and the stresses</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3961,23 +4035,23 @@
         </is>
       </c>
       <c r="C5" s="8">
-        <f>DCF!C54</f>
+        <f>DCF!C62</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  backlog run-off alternative</t>
+          <t xml:space="preserve">  run-off stress</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>new sales halve and fade; margins compress (engine re-run)</t>
+          <t>launches halve and fade (engine re-run; vectors on Assumptions)</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>4.179391161327742</v>
+        <v>3.784078327184524</v>
       </c>
     </row>
     <row r="7">
@@ -3988,11 +4062,11 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>sales hold at AED 30bn; margins hold (engine re-run)</t>
+          <t>sales hold near the realised pace (engine re-run)</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>7.393430194946205</v>
+        <v>6.305618176058718</v>
       </c>
     </row>
     <row r="8">
@@ -4003,158 +4077,173 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>non-UAE revenue share carries the Egypt country premium (engine re-run)</t>
+          <t>non-UAE revenue share carries the Egypt premium (engine re-run)</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>5.086676693032556</v>
+        <v>4.311736370448707</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Relative multiples</t>
+          <t xml:space="preserve">  gross-cash bridge alternative</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>justified P/E and EV/EBITDA against the UAE developer set</t>
-        </is>
-      </c>
-      <c r="C9" s="8">
-        <f>'Relative &amp; Normalized'!C11</f>
-        <v/>
+          <t>escrow/restricted cash included (engine re-run)</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>5.520395478237414</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Normalised earnings power</t>
+          <t>Relative multiples</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>through-cycle sales and margin at a through-cycle multiple</t>
+          <t>justified P/E vs the rebuilt attributable peer set</t>
         </is>
       </c>
       <c r="C10" s="8">
-        <f>'Relative &amp; Normalized'!C28</f>
+        <f>'Relative &amp; Normalized'!C11</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
+          <t>Normalised earnings power</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>through-cycle sales, margin, multiple</t>
+        </is>
+      </c>
+      <c r="C11" s="8">
+        <f>'Relative &amp; Normalized'!C28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
           <t>Book value and sustainable return</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>justified price-to-book on sustainable return on equity</t>
-        </is>
-      </c>
-      <c r="C11" s="8">
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>justified P/B on sustainable ROE, rolled</t>
+        </is>
+      </c>
+      <c r="C12" s="8">
         <f>'Relative &amp; Normalized'!C36</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Weighted central (links to Summary)</t>
         </is>
       </c>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="13">
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="13">
         <f>Summary!C9</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>What the market price implies</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>cost-of-equity adder that reconciles the base DCF to spot (engine solve)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="n">
-        <v>0.1140908329246707</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>cost-of-equity adder reconciling the base DCF to spot (engine solve)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="n">
+        <v>0.06180334991240068</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Expert panel (engine re-runs, worked in Appendix C)</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>AED per share</t>
         </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Expert 1</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>asset value (RNAV)</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>3.923210931248883</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Expert 2</t>
+          <t>Expert 1</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>owner cash flow, run-off basis</t>
+          <t>asset value (RNAV)</t>
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>4.05809229633167</v>
+        <v>4.058071128115847</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
+          <t>Expert 2</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>owner cash flow, run-off stress basis</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>3.619591626807453</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
           <t>Expert 3</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>peer-multiple convergence</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
-        <v>1.737438233090195</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="C21" s="7" t="n">
+        <v>1.814855425613052</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>Panel median</t>
         </is>
       </c>
-      <c r="C21" s="23">
-        <f>MEDIAN(C18:C20)</f>
+      <c r="C22" s="23">
+        <f>MEDIAN(C19:C21)</f>
         <v/>
       </c>
     </row>
@@ -4169,7 +4258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -4199,7 +4288,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Vectors run FY2026E..FY2030E across columns C..G</t>
+          <t>Vectors run H2-2026E..FY2030E across columns C..G; scenario vectors at the foot are published for reproducibility of the pasted engine outputs</t>
         </is>
       </c>
     </row>
@@ -4212,7 +4301,7 @@
       <c r="B3" s="5" t="inlineStr"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>FY26E / value</t>
+          <t>H2-26E / value</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -4257,757 +4346,1165 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Backlog conversion rate on opening development backlog</t>
-        </is>
-      </c>
-      <c r="C6" s="24" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="D6" s="24" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E6" s="24" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="F6" s="24" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="G6" s="24" t="n">
-        <v>0.33</v>
-      </c>
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 anchors (reviewed interim + results release, pasted)</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>New development sales (AED mn)</t>
+          <t>Development backlog at 30-Jun-2026 (65.4bn × 95%, disclosed)</t>
         </is>
       </c>
       <c r="C7" s="19" t="n">
-        <v>26000</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>24000</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>22000</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>20500</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>19000</v>
+        <v>62130</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Land and plot sales revenue (AED mn)</t>
+          <t>Unrestricted (available) cash at 30-Jun-2026 (disclosed)</t>
         </is>
       </c>
       <c r="C8" s="19" t="n">
-        <v>1800</v>
-      </c>
-      <c r="D8" s="19" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E8" s="19" t="n">
-        <v>1400</v>
-      </c>
-      <c r="F8" s="19" t="n">
-        <v>1200</v>
-      </c>
-      <c r="G8" s="19" t="n">
-        <v>1000</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Development gross margin</t>
-        </is>
-      </c>
-      <c r="C9" s="24" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="D9" s="24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E9" s="24" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="F9" s="24" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="G9" s="24" t="n">
-        <v>0.38</v>
+          <t>Total cash and bank balances at 30-Jun-2026 (disclosed)</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>12303.24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Asset &amp; investment management revenue growth</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D10" s="24" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="E10" s="24" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="F10" s="24" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G10" s="24" t="n">
-        <v>0.08</v>
+          <t>Gross debt incl. related-party loan at 30-Jun-2026 (disclosed)</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>9541.684999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Asset &amp; investment management gross margin</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="D11" s="24" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E11" s="24" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="F11" s="24" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="G11" s="24" t="n">
-        <v>0.64</v>
+          <t>Lease liabilities at 30-Jun-2026 (disclosed)</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>644.799</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Hospitality revenue growth</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D12" s="24" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E12" s="24" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F12" s="24" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G12" s="24" t="n">
-        <v>0.06</v>
+          <t>Associates &amp; JVs at carrying value, 30-Jun-2026 (disclosed)</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>2826.454</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Hospitality gross margin</t>
-        </is>
-      </c>
-      <c r="C13" s="24" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="D13" s="24" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E13" s="24" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="F13" s="24" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G13" s="24" t="n">
-        <v>0.3</v>
+          <t>Investments in financial assets, 30-Jun-2026 (disclosed)</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>392.972</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Events, catering &amp; tourism revenue growth</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="D14" s="24" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E14" s="24" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="F14" s="24" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="G14" s="24" t="n">
-        <v>0.039</v>
+          <t>Non-controlling interests, 30-Jun-2026 (disclosed)</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>922.342</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Events, catering &amp; tourism gross margin</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="D15" s="24" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="G15" s="24" t="n">
-        <v>0.28</v>
+          <t>Equity attributable to owners, 30-Jun-2026 (disclosed)</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>56396.629</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Others / eliminations revenue (AED mn)</t>
+          <t>Receivables incl. related-party, 30-Jun-2026 (disclosed)</t>
         </is>
       </c>
       <c r="C16" s="19" t="n">
-        <v>-30</v>
+        <v>22155.68</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Others gross loss (AED mn)</t>
+          <t>Inventories + development WIP, 30-Jun-2026 (disclosed)</t>
         </is>
       </c>
       <c r="C17" s="19" t="n">
-        <v>-120</v>
+        <v>34087.289</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>General &amp; administrative / revenue</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="D18" s="24" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="E18" s="24" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>0.08500000000000001</v>
+          <t>Payables incl. advances + related-party, 30-Jun-2026 (disclosed)</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>22289.32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Selling &amp; marketing / revenue</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="D19" s="24" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="G19" s="24" t="n">
-        <v>0.016</v>
+          <t>H1-2026 revenue (actual)</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>9188.304</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Investment and other income, recurring (AED mn)</t>
+          <t>H1-2026 gross profit (actual)</t>
         </is>
       </c>
       <c r="C20" s="19" t="n">
-        <v>160</v>
-      </c>
-      <c r="D20" s="19" t="n">
-        <v>165</v>
-      </c>
-      <c r="E20" s="19" t="n">
-        <v>170</v>
-      </c>
-      <c r="F20" s="19" t="n">
-        <v>175</v>
-      </c>
-      <c r="G20" s="19" t="n">
-        <v>180</v>
+        <v>3201.275</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Depreciation &amp; amortisation / revenue</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="n">
-        <v>0.042</v>
+          <t>H1-2026 attributable profit (actual)</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>2162.966</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Capital expenditure (AED mn)</t>
+          <t>H1-2026 adjusted EBITDA (disclosed)</t>
         </is>
       </c>
       <c r="C22" s="19" t="n">
-        <v>1400</v>
-      </c>
-      <c r="D22" s="19" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E22" s="19" t="n">
-        <v>1550</v>
-      </c>
-      <c r="F22" s="19" t="n">
-        <v>1600</v>
-      </c>
-      <c r="G22" s="19" t="n">
-        <v>1650</v>
+        <v>2995</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Working-capital release, negative = absorption (AED mn)</t>
+          <t>Depreciable asset base at 30-Jun-2026 (PP&amp;E+IP+ROU+intangibles)</t>
         </is>
       </c>
       <c r="C23" s="19" t="n">
-        <v>-1500</v>
-      </c>
-      <c r="D23" s="19" t="n">
-        <v>800</v>
-      </c>
-      <c r="E23" s="19" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F23" s="19" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G23" s="19" t="n">
-        <v>1400</v>
+        <v>19736.134</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Effective tax rate (DMTT floor + foreign uplift)</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="n">
-        <v>0.155</v>
-      </c>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Forecast drivers (H2-2026 stub, then annual)</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
+      <c r="H24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>NCI share of profit</t>
+          <t>Backlog conversion rate on opening development backlog</t>
         </is>
       </c>
       <c r="C25" s="24" t="n">
-        <v>0.02</v>
+        <v>0.105</v>
+      </c>
+      <c r="D25" s="24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E25" s="24" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F25" s="24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G25" s="24" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Associate income FY2026E base (AED mn)</t>
+          <t>New development sales (AED mn)</t>
         </is>
       </c>
       <c r="C26" s="19" t="n">
-        <v>200</v>
+        <v>12000</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>23000</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>21000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Associate income growth</t>
-        </is>
-      </c>
-      <c r="C27" s="24" t="n">
-        <v>0.08</v>
+          <t>Land and plot sales revenue (AED mn)</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="n">
+        <v>700</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F27" s="19" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>1100</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Gross debt path incl. related-party loan (AED mn)</t>
-        </is>
-      </c>
-      <c r="C28" s="19" t="n">
-        <v>9700</v>
-      </c>
-      <c r="D28" s="19" t="n">
-        <v>9900</v>
-      </c>
-      <c r="E28" s="19" t="n">
-        <v>9200</v>
-      </c>
-      <c r="F28" s="19" t="n">
-        <v>8300</v>
-      </c>
-      <c r="G28" s="19" t="n">
-        <v>7400</v>
+          <t>Development gross margin</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="D28" s="24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E28" s="24" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F28" s="24" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="G28" s="24" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Yield on cash balances</t>
+          <t>Asset &amp; investment management growth (from FY27)</t>
         </is>
       </c>
       <c r="C29" s="24" t="n">
-        <v>0.035</v>
+        <v>0</v>
+      </c>
+      <c r="D29" s="24" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E29" s="24" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="F29" s="24" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G29" s="24" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Cost of capital build</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="n"/>
-      <c r="C30" s="15" t="n"/>
-      <c r="D30" s="15" t="n"/>
-      <c r="E30" s="15" t="n"/>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
-      <c r="H30" s="15" t="n"/>
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Asset &amp; investment management H2-2026E revenue</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="n">
+        <v>385</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>AED government bond yield (Jan-2031 T-Bond auction)</t>
-        </is>
-      </c>
-      <c r="C31" s="21" t="n">
-        <v>0.0448</v>
+          <t>Asset &amp; investment management gross margin</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D31" s="24" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E31" s="24" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F31" s="24" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G31" s="24" t="n">
+        <v>0.64</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>UAE sovereign default spread (rating basis, netted out)</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="n">
-        <v>0.0042</v>
+          <t>Hospitality growth (from FY27)</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="24" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E32" s="24" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F32" s="24" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G32" s="24" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Equity risk premium (UAE row, rating basis)</t>
-        </is>
-      </c>
-      <c r="C33" s="21" t="n">
-        <v>0.0487</v>
+          <t>Hospitality H2-2026E revenue</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="n">
+        <v>452</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Beta (tier-3 fallback, flagged; sensitised 0.8-1.2)</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>1</v>
+          <t>Hospitality gross margin</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D34" s="24" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E34" s="24" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F34" s="24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G34" s="24" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>6-month EIBOR</t>
-        </is>
-      </c>
-      <c r="C35" s="21" t="n">
-        <v>0.0371</v>
+          <t>Events, catering &amp; tourism growth (from FY27)</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="24" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E35" s="24" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="F35" s="24" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="G35" s="24" t="n">
+        <v>0.039</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Marginal debt margin over 6M EIBOR</t>
-        </is>
-      </c>
-      <c r="C36" s="21" t="n">
-        <v>0.0165</v>
+          <t>Events, catering &amp; tourism H2-2026E revenue</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="n">
+        <v>3000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Terminal debt weight D/(D+E)</t>
+          <t>Events, catering &amp; tourism gross margin</t>
         </is>
       </c>
       <c r="C37" s="24" t="n">
-        <v>0.15</v>
+        <v>0.29</v>
+      </c>
+      <c r="D37" s="24" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E37" s="24" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="F37" s="24" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G37" s="24" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="C38" s="21" t="n">
-        <v>0.025</v>
+          <t>H1-2026 AIM revenue (actual)</t>
+        </is>
+      </c>
+      <c r="C38" s="19" t="n">
+        <v>360.966</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital</t>
-        </is>
-      </c>
-      <c r="C39" s="21" t="n">
-        <v>0.08500000000000001</v>
+          <t>H1-2026 Hospitality revenue (actual)</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="n">
+        <v>388.398</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Days from 31-Dec-2025 valuation date to the 7-Aug-2026 anchor</t>
+          <t>H1-2026 ECT revenue (actual)</t>
         </is>
       </c>
       <c r="C40" s="19" t="n">
-        <v>219</v>
+        <v>2775.402</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>FY2025 balance-sheet anchors (audited, pasted)</t>
-        </is>
-      </c>
-      <c r="B41" s="15" t="n"/>
-      <c r="C41" s="15" t="n"/>
-      <c r="D41" s="15" t="n"/>
-      <c r="E41" s="15" t="n"/>
-      <c r="F41" s="15" t="n"/>
-      <c r="G41" s="15" t="n"/>
-      <c r="H41" s="15" t="n"/>
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Others / eliminations revenue (full-year rate)</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="n">
+        <v>-30</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Cash and bank balances FY2025 (AED mn, disclosed)</t>
+          <t>Others gross loss (full-year rate)</t>
         </is>
       </c>
       <c r="C42" s="19" t="n">
-        <v>12641.987</v>
+        <v>-120</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Gross debt FY2025 incl. related-party loan (AED mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C43" s="19" t="n">
-        <v>6789.085999999999</v>
+          <t>General &amp; administrative / revenue</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="D43" s="24" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="E43" s="24" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="F43" s="24" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="G43" s="24" t="n">
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Lease liabilities FY2025 (AED mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C44" s="19" t="n">
-        <v>623.7660000000001</v>
+          <t>Selling &amp; marketing / revenue</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="D44" s="24" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E44" s="24" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="F44" s="24" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="G44" s="24" t="n">
+        <v>0.016</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Associates &amp; JVs at carrying value FY2025 (AED mn, disclosed)</t>
+          <t>Investment and other income, recurring (AED mn)</t>
         </is>
       </c>
       <c r="C45" s="19" t="n">
-        <v>3723.897</v>
+        <v>80</v>
+      </c>
+      <c r="D45" s="19" t="n">
+        <v>165</v>
+      </c>
+      <c r="E45" s="19" t="n">
+        <v>170</v>
+      </c>
+      <c r="F45" s="19" t="n">
+        <v>175</v>
+      </c>
+      <c r="G45" s="19" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Investments in financial assets FY2025 (AED mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C46" s="19" t="n">
-        <v>394.305</v>
+          <t>D&amp;A rate on the average depreciable asset base</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n">
+        <v>0.034</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Non-controlling interests FY2025 (AED mn, disclosed)</t>
+          <t>Capital expenditure (AED mn)</t>
         </is>
       </c>
       <c r="C47" s="19" t="n">
-        <v>847.48</v>
+        <v>700</v>
+      </c>
+      <c r="D47" s="19" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E47" s="19" t="n">
+        <v>1550</v>
+      </c>
+      <c r="F47" s="19" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G47" s="19" t="n">
+        <v>1650</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Equity attributable to owners FY2025 (AED mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C48" s="19" t="n">
-        <v>53902.504</v>
+          <t>Effective tax rate (DMTT floor + foreign uplift)</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="n">
+        <v>0.155</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Development backlog at 31-Dec-2025 (AED mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C49" s="19" t="n">
-        <v>42600</v>
+          <t>NCI share of profit</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>Lens settings</t>
-        </is>
-      </c>
-      <c r="B50" s="15" t="n"/>
-      <c r="C50" s="15" t="n"/>
-      <c r="D50" s="15" t="n"/>
-      <c r="E50" s="15" t="n"/>
-      <c r="F50" s="15" t="n"/>
-      <c r="G50" s="15" t="n"/>
-      <c r="H50" s="15" t="n"/>
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Associate income path (AED mn)</t>
+        </is>
+      </c>
+      <c r="C50" s="19" t="n">
+        <v>95</v>
+      </c>
+      <c r="D50" s="19" t="n">
+        <v>210</v>
+      </c>
+      <c r="E50" s="19" t="n">
+        <v>227</v>
+      </c>
+      <c r="F50" s="19" t="n">
+        <v>245</v>
+      </c>
+      <c r="G50" s="19" t="n">
+        <v>264</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Justified price/earnings (FY2026E attributable)</t>
-        </is>
-      </c>
-      <c r="C51" s="25" t="n">
-        <v>8</v>
+          <t>Gross debt path incl. related-party loan (AED mn)</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="n">
+        <v>10300</v>
+      </c>
+      <c r="D51" s="19" t="n">
+        <v>10500</v>
+      </c>
+      <c r="E51" s="19" t="n">
+        <v>9700</v>
+      </c>
+      <c r="F51" s="19" t="n">
+        <v>8800</v>
+      </c>
+      <c r="G51" s="19" t="n">
+        <v>7900</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA (FY2026E)</t>
-        </is>
-      </c>
-      <c r="C52" s="25" t="n">
-        <v>7</v>
+          <t>Yield on cash balances</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="n">
+        <v>0.035</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Through-cycle development sales (AED mn)</t>
+          <t>Interest on lease liabilities (AED mn/yr)</t>
         </is>
       </c>
       <c r="C53" s="19" t="n">
-        <v>18000</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Through-cycle net margin on revenue</t>
-        </is>
-      </c>
-      <c r="C54" s="24" t="n">
-        <v>0.115</v>
-      </c>
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>Working capital components (calibrated 31-Dec-25 and 30-Jun-26)</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="n"/>
+      <c r="C54" s="15" t="n"/>
+      <c r="D54" s="15" t="n"/>
+      <c r="E54" s="15" t="n"/>
+      <c r="F54" s="15" t="n"/>
+      <c r="G54" s="15" t="n"/>
+      <c r="H54" s="15" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>Through-cycle price/earnings</t>
-        </is>
-      </c>
-      <c r="C55" s="25" t="n">
-        <v>8.5</v>
+          <t>Receivable days (incl. related-party) on revenue</t>
+        </is>
+      </c>
+      <c r="C55" s="19" t="n">
+        <v>440</v>
+      </c>
+      <c r="D55" s="19" t="n">
+        <v>430</v>
+      </c>
+      <c r="E55" s="19" t="n">
+        <v>410</v>
+      </c>
+      <c r="F55" s="19" t="n">
+        <v>390</v>
+      </c>
+      <c r="G55" s="19" t="n">
+        <v>370</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Sustainable return on equity</t>
+          <t>New WIP added per AED of new development sales</t>
         </is>
       </c>
       <c r="C56" s="24" t="n">
-        <v>0.075</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Weight — discounted cash flow</t>
+          <t>Land-bank/WIP share of development cost of sales</t>
         </is>
       </c>
       <c r="C57" s="24" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>Weight — relative</t>
-        </is>
-      </c>
-      <c r="C58" s="24" t="n">
-        <v>0.2</v>
+          <t>Payables + advances cover of annual direct costs (×)</t>
+        </is>
+      </c>
+      <c r="C58" s="25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="D58" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E58" s="25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F58" s="25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G58" s="25" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>Weight — normalised</t>
-        </is>
-      </c>
-      <c r="C59" s="24" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>Cost of capital build</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="n"/>
+      <c r="C59" s="15" t="n"/>
+      <c r="D59" s="15" t="n"/>
+      <c r="E59" s="15" t="n"/>
+      <c r="F59" s="15" t="n"/>
+      <c r="G59" s="15" t="n"/>
+      <c r="H59" s="15" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
+          <t>AED government bond yield (Jan-2031 T-Bond auction)</t>
+        </is>
+      </c>
+      <c r="C60" s="21" t="n">
+        <v>0.0448</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>UAE sovereign default spread (rating basis, netted out)</t>
+        </is>
+      </c>
+      <c r="C61" s="21" t="n">
+        <v>0.0042</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Equity risk premium (UAE row, rating basis)</t>
+        </is>
+      </c>
+      <c r="C62" s="21" t="n">
+        <v>0.0487</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Beta (own-stock regression vs equal-weight AE panel proxy)</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>6-month EIBOR (31-Mar-2026 fixing, dated)</t>
+        </is>
+      </c>
+      <c r="C64" s="21" t="n">
+        <v>0.0371</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Marginal debt margin over 6M EIBOR</t>
+        </is>
+      </c>
+      <c r="C65" s="21" t="n">
+        <v>0.0165</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="C66" s="21" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Terminal return on invested capital</t>
+        </is>
+      </c>
+      <c r="C67" s="21" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Days from the 30-Jun-2026 valuation date to the 7-Aug anchor</t>
+        </is>
+      </c>
+      <c r="C68" s="19" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>FY2025 disclosed anchors (audited, pasted)</t>
+        </is>
+      </c>
+      <c r="B69" s="15" t="n"/>
+      <c r="C69" s="15" t="n"/>
+      <c r="D69" s="15" t="n"/>
+      <c r="E69" s="15" t="n"/>
+      <c r="F69" s="15" t="n"/>
+      <c r="G69" s="15" t="n"/>
+      <c r="H69" s="15" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 profit for the year (AED mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C70" s="19" t="n">
+        <v>3925.705</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 attributable profit (AED mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C71" s="19" t="n">
+        <v>4020.102</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 EBITDA, house basis = EBIT + D&amp;A (AED mn)</t>
+        </is>
+      </c>
+      <c r="C72" s="19" t="n">
+        <v>4895.552000000001</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 net debt, strict basis (AED mn)</t>
+        </is>
+      </c>
+      <c r="C73" s="19" t="n">
+        <v>-5852.901</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>Lens settings</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="n"/>
+      <c r="C74" s="15" t="n"/>
+      <c r="D74" s="15" t="n"/>
+      <c r="E74" s="15" t="n"/>
+      <c r="F74" s="15" t="n"/>
+      <c r="G74" s="15" t="n"/>
+      <c r="H74" s="15" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Justified price/earnings (FY2026E attributable)</t>
+        </is>
+      </c>
+      <c r="C75" s="25" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>EV/EBITDA cross-check multiple (house judgement, unanchored)</t>
+        </is>
+      </c>
+      <c r="C76" s="25" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Through-cycle development sales (AED mn)</t>
+        </is>
+      </c>
+      <c r="C77" s="19" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Through-cycle net margin on revenue</t>
+        </is>
+      </c>
+      <c r="C78" s="24" t="n">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Recurring-legs revenue base, FY2025 (AED mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C79" s="19" t="n">
+        <v>6455.178</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Through-cycle price/earnings</t>
+        </is>
+      </c>
+      <c r="C80" s="25" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Sustainable return on equity</t>
+        </is>
+      </c>
+      <c r="C81" s="24" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Weight — discounted cash flow</t>
+        </is>
+      </c>
+      <c r="C82" s="24" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>Weight — relative</t>
+        </is>
+      </c>
+      <c r="C83" s="24" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>Weight — normalised</t>
+        </is>
+      </c>
+      <c r="C84" s="24" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
           <t>Weight — book</t>
         </is>
       </c>
-      <c r="C60" s="24" t="n">
+      <c r="C85" s="24" t="n">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>Scenario driver vectors (engine re-run inputs, published for reproducibility — the pasted scenario outputs use exactly these)</t>
+        </is>
+      </c>
+      <c r="B86" s="15" t="n"/>
+      <c r="C86" s="15" t="n"/>
+      <c r="D86" s="15" t="n"/>
+      <c r="E86" s="15" t="n"/>
+      <c r="F86" s="15" t="n"/>
+      <c r="G86" s="15" t="n"/>
+      <c r="H86" s="15" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>scenario: run-off new development sales</t>
+        </is>
+      </c>
+      <c r="C87" s="19" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D87" s="19" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E87" s="19" t="n">
+        <v>11000</v>
+      </c>
+      <c r="F87" s="19" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G87" s="19" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>scenario: run-off development margin</t>
+        </is>
+      </c>
+      <c r="C88" s="24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D88" s="24" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E88" s="24" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F88" s="24" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G88" s="24" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>scenario: growth-hold new development sales</t>
+        </is>
+      </c>
+      <c r="C89" s="19" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D89" s="19" t="n">
+        <v>34000</v>
+      </c>
+      <c r="E89" s="19" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F89" s="19" t="n">
+        <v>34000</v>
+      </c>
+      <c r="G89" s="19" t="n">
+        <v>34000</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>scenario: growth-hold development margin</t>
+        </is>
+      </c>
+      <c r="C90" s="24" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D90" s="24" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E90" s="24" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F90" s="24" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G90" s="24" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>scenario: Egypt stress — non-UAE revenue share (note 5)</t>
+        </is>
+      </c>
+      <c r="C91" s="24" t="n">
+        <v>0.170797409390457</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>scenario: Egypt country risk premium (Damodaran)</t>
+        </is>
+      </c>
+      <c r="C92" s="21" t="n">
+        <v>0.09710000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -5021,7 +5518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5035,7 +5532,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SOTP bridge — segment EV split and the EV → equity walk</t>
+          <t>SOTP bridge — segment EV split (weights DERIVED) and the EV → equity walk</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5047,220 +5544,234 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>The four legs share one AED discount rate; the Egypt stress prices the cross-border leg separately</t>
+          <t>Weight = FY2025 segment gross profit less a revenue-proportional corporate load — all live formulas off Segments and the FY2025 disclosed opex</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 G&amp;A + S&amp;M (audited, for the load allocation)</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n">
+        <v>1813.687</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Enterprise value by segment</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Weight base (FY2025 GP less corporate load)</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Weight (GP − load share)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>AED mn</t>
         </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Real Estate Development</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="n">
-        <v>2261.929994799141</v>
-      </c>
-      <c r="C5" s="17">
-        <f>MAX(B5,0)/3372.324009*DCF!C41</f>
-        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Asset &amp; Investment Management</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="n">
-        <v>335.223143778497</v>
+          <t>Real Estate Development</t>
+        </is>
+      </c>
+      <c r="B6" s="17">
+        <f>Segments!C5-$B$4*Segments!B5/Segments!B10</f>
+        <v/>
       </c>
       <c r="C6" s="17">
-        <f>MAX(B6,0)/3372.324009*DCF!C41</f>
+        <f>MAX(B6,0)/(MAX(B$6,0)+MAX(B$7,0)+MAX(B$8,0)+MAX(B$9,0))*DCF!C48</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Hospitality</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="n">
-        <v>107.0504681431287</v>
+          <t>Asset &amp; Investment Management</t>
+        </is>
+      </c>
+      <c r="B7" s="17">
+        <f>Segments!C6-$B$4*Segments!B6/Segments!B10</f>
+        <v/>
       </c>
       <c r="C7" s="17">
-        <f>MAX(B7,0)/3372.324009*DCF!C41</f>
+        <f>MAX(B7,0)/(MAX(B$6,0)+MAX(B$7,0)+MAX(B$8,0)+MAX(B$9,0))*DCF!C48</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="B8" s="17">
+        <f>Segments!C7-$B$4*Segments!B7/Segments!B10</f>
+        <v/>
+      </c>
+      <c r="C8" s="17">
+        <f>MAX(B8,0)/(MAX(B$6,0)+MAX(B$7,0)+MAX(B$8,0)+MAX(B$9,0))*DCF!C48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
           <t>Events, Catering &amp; Tourism</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n">
-        <v>668.1204019387269</v>
-      </c>
-      <c r="C8" s="17">
-        <f>MAX(B8,0)/3372.324009*DCF!C41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="B9" s="17">
+        <f>Segments!C8-$B$4*Segments!B8/Segments!B10</f>
+        <v/>
+      </c>
+      <c r="C9" s="17">
+        <f>MAX(B9,0)/(MAX(B$6,0)+MAX(B$7,0)+MAX(B$8,0)+MAX(B$9,0))*DCF!C48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Enterprise value (links to DCF)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n"/>
-      <c r="C9" s="26">
-        <f>DCF!C41</f>
-        <v/>
-      </c>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="15" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Terminal value share of enterprise value</t>
-        </is>
-      </c>
-      <c r="C10" s="11">
-        <f>DCF!C42</f>
-        <v/>
-      </c>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="26">
+        <f>DCF!C48</f>
+        <v/>
+      </c>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>+ Cash and bank balances</t>
-        </is>
-      </c>
-      <c r="C11" s="18">
-        <f>Assumptions!$C$42</f>
+          <t>Terminal value share of enterprise value</t>
+        </is>
+      </c>
+      <c r="C11" s="11">
+        <f>DCF!C49</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>− Gross debt incl. related-party loan</t>
+          <t>+ Unrestricted cash (disclosed)</t>
         </is>
       </c>
       <c r="C12" s="18">
-        <f>-Assumptions!$C$43</f>
+        <f>Assumptions!$C$8</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>− Lease liabilities</t>
+          <t>− Gross debt incl. related-party loan</t>
         </is>
       </c>
       <c r="C13" s="18">
-        <f>-Assumptions!$C$44</f>
+        <f>-Assumptions!$C$10</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>+ Associates &amp; JVs</t>
+          <t>− Lease liabilities</t>
         </is>
       </c>
       <c r="C14" s="18">
-        <f>Assumptions!$C$45</f>
+        <f>-Assumptions!$C$11</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>+ Financial assets</t>
+          <t>+ Associates &amp; JVs</t>
         </is>
       </c>
       <c r="C15" s="18">
-        <f>Assumptions!$C$46</f>
+        <f>Assumptions!$C$12</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>− Non-controlling interests (book)</t>
+          <t>+ Financial assets</t>
         </is>
       </c>
       <c r="C16" s="18">
-        <f>-Assumptions!$C$47</f>
+        <f>Assumptions!$C$13</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>− NCI (capitalised, links to DCF)</t>
+        </is>
+      </c>
+      <c r="C17" s="18">
+        <f>DCF!C58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Equity attributable → per share → at anchor</t>
         </is>
       </c>
-      <c r="B17" s="15" t="n"/>
-      <c r="C17" s="26">
-        <f>C9+SUM(C11:C16)</f>
-        <v/>
-      </c>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="15" t="n"/>
-      <c r="F17" s="15" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>per share, 31-Dec-2025</t>
-        </is>
-      </c>
-      <c r="C18" s="10">
-        <f>C17/Assumptions!$C$5</f>
-        <v/>
-      </c>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="26">
+        <f>C10+SUM(C12:C17)</f>
+        <v/>
+      </c>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
+          <t>per share, 30-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C19" s="10">
+        <f>C18/Assumptions!$C$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
           <t>per share at the 7-Aug-2026 anchor</t>
         </is>
       </c>
-      <c r="C19" s="23">
-        <f>C18*DCF!C53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>NCI alternative framing (capitalised at share of profit, engine)</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="n">
-        <v>5.958324419657603</v>
+      <c r="C20" s="23">
+        <f>C19*DCF!C61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Book-NCI alternative framing (engine)</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>5.341697814358385</v>
       </c>
     </row>
   </sheetData>
@@ -5290,7 +5801,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Segments — the four disclosed legs, FY2025 base and forecast build</t>
+          <t>Segments — FY2025 base, H1-2026 actuals, and the forecast build</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5304,7 +5815,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>FY2025 base pasted from IFRS 8 note 33 (audited); every forecast cell is a formula off Assumptions</t>
+          <t>FY2025 base and H1-2026 actuals pasted (disclosed); every forecast cell is a formula off Assumptions</t>
         </is>
       </c>
     </row>
@@ -5468,12 +5979,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Development build</t>
+          <t>Development build (from the 30-Jun-2026 disclosed backlog)</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>FY26E</t>
+          <t>H2-26E</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -5504,7 +6015,7 @@
         </is>
       </c>
       <c r="B13" s="18">
-        <f>Assumptions!$C$49</f>
+        <f>Assumptions!$C$7</f>
         <v/>
       </c>
       <c r="C13" s="17">
@@ -5531,23 +6042,23 @@
         </is>
       </c>
       <c r="B14" s="18">
-        <f>Assumptions!$C$7</f>
+        <f>Assumptions!$C$26</f>
         <v/>
       </c>
       <c r="C14" s="18">
-        <f>Assumptions!$D$7</f>
+        <f>Assumptions!$D$26</f>
         <v/>
       </c>
       <c r="D14" s="18">
-        <f>Assumptions!$E$7</f>
+        <f>Assumptions!$E$26</f>
         <v/>
       </c>
       <c r="E14" s="18">
-        <f>Assumptions!$F$7</f>
+        <f>Assumptions!$F$26</f>
         <v/>
       </c>
       <c r="F14" s="18">
-        <f>Assumptions!$G$7</f>
+        <f>Assumptions!$G$26</f>
         <v/>
       </c>
     </row>
@@ -5558,23 +6069,23 @@
         </is>
       </c>
       <c r="B15" s="17">
-        <f>Assumptions!$C$6*B13</f>
+        <f>Assumptions!$C$25*B13</f>
         <v/>
       </c>
       <c r="C15" s="17">
-        <f>Assumptions!$D$6*C13</f>
+        <f>Assumptions!$D$25*C13</f>
         <v/>
       </c>
       <c r="D15" s="17">
-        <f>Assumptions!$E$6*D13</f>
+        <f>Assumptions!$E$25*D13</f>
         <v/>
       </c>
       <c r="E15" s="17">
-        <f>Assumptions!$F$6*E13</f>
+        <f>Assumptions!$F$25*E13</f>
         <v/>
       </c>
       <c r="F15" s="17">
-        <f>Assumptions!$G$6*F13</f>
+        <f>Assumptions!$G$25*F13</f>
         <v/>
       </c>
     </row>
@@ -5612,23 +6123,23 @@
         </is>
       </c>
       <c r="B17" s="18">
-        <f>Assumptions!$C$8</f>
+        <f>Assumptions!$C$27</f>
         <v/>
       </c>
       <c r="C17" s="18">
-        <f>Assumptions!$D$8</f>
+        <f>Assumptions!$D$27</f>
         <v/>
       </c>
       <c r="D17" s="18">
-        <f>Assumptions!$E$8</f>
+        <f>Assumptions!$E$27</f>
         <v/>
       </c>
       <c r="E17" s="18">
-        <f>Assumptions!$F$8</f>
+        <f>Assumptions!$F$27</f>
         <v/>
       </c>
       <c r="F17" s="18">
-        <f>Assumptions!$G$8</f>
+        <f>Assumptions!$G$27</f>
         <v/>
       </c>
     </row>
@@ -5667,7 +6178,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>FY26E</t>
+          <t>H2-26E</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -5724,24 +6235,24 @@
           <t>Asset &amp; Investment Management</t>
         </is>
       </c>
-      <c r="B22" s="17">
-        <f>B6*(1+Assumptions!$C$10)</f>
+      <c r="B22" s="18">
+        <f>Assumptions!$C$30</f>
         <v/>
       </c>
       <c r="C22" s="17">
-        <f>B22*(1+Assumptions!$D$10)</f>
+        <f>(Assumptions!$C$38+Assumptions!$C$30)*(1+Assumptions!$D$29)</f>
         <v/>
       </c>
       <c r="D22" s="17">
-        <f>C22*(1+Assumptions!$E$10)</f>
+        <f>C22*(1+Assumptions!$E$29)</f>
         <v/>
       </c>
       <c r="E22" s="17">
-        <f>D22*(1+Assumptions!$F$10)</f>
+        <f>D22*(1+Assumptions!$F$29)</f>
         <v/>
       </c>
       <c r="F22" s="17">
-        <f>E22*(1+Assumptions!$G$10)</f>
+        <f>E22*(1+Assumptions!$G$29)</f>
         <v/>
       </c>
     </row>
@@ -5751,24 +6262,24 @@
           <t>Hospitality</t>
         </is>
       </c>
-      <c r="B23" s="17">
-        <f>B7*(1+Assumptions!$C$12)</f>
+      <c r="B23" s="18">
+        <f>Assumptions!$C$33</f>
         <v/>
       </c>
       <c r="C23" s="17">
-        <f>B23*(1+Assumptions!$D$12)</f>
+        <f>(Assumptions!$C$39+Assumptions!$C$33)*(1+Assumptions!$D$32)</f>
         <v/>
       </c>
       <c r="D23" s="17">
-        <f>C23*(1+Assumptions!$E$12)</f>
+        <f>C23*(1+Assumptions!$E$32)</f>
         <v/>
       </c>
       <c r="E23" s="17">
-        <f>D23*(1+Assumptions!$F$12)</f>
+        <f>D23*(1+Assumptions!$F$32)</f>
         <v/>
       </c>
       <c r="F23" s="17">
-        <f>E23*(1+Assumptions!$G$12)</f>
+        <f>E23*(1+Assumptions!$G$32)</f>
         <v/>
       </c>
     </row>
@@ -5778,51 +6289,51 @@
           <t>Events, Catering &amp; Tourism</t>
         </is>
       </c>
-      <c r="B24" s="17">
-        <f>B8*(1+Assumptions!$C$14)</f>
+      <c r="B24" s="18">
+        <f>Assumptions!$C$36</f>
         <v/>
       </c>
       <c r="C24" s="17">
-        <f>B24*(1+Assumptions!$D$14)</f>
+        <f>(Assumptions!$C$40+Assumptions!$C$36)*(1+Assumptions!$D$35)</f>
         <v/>
       </c>
       <c r="D24" s="17">
-        <f>C24*(1+Assumptions!$E$14)</f>
+        <f>C24*(1+Assumptions!$E$35)</f>
         <v/>
       </c>
       <c r="E24" s="17">
-        <f>D24*(1+Assumptions!$F$14)</f>
+        <f>D24*(1+Assumptions!$F$35)</f>
         <v/>
       </c>
       <c r="F24" s="17">
-        <f>E24*(1+Assumptions!$G$14)</f>
+        <f>E24*(1+Assumptions!$G$35)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Others / eliminations</t>
+          <t>Others / eliminations (half-year in the stub)</t>
         </is>
       </c>
       <c r="B25" s="18">
-        <f>Assumptions!$C$16</f>
+        <f>Assumptions!$C$41*0.5</f>
         <v/>
       </c>
       <c r="C25" s="18">
-        <f>Assumptions!$C$16</f>
+        <f>Assumptions!$C$41*1.0</f>
         <v/>
       </c>
       <c r="D25" s="18">
-        <f>Assumptions!$C$16</f>
+        <f>Assumptions!$C$41*1.0</f>
         <v/>
       </c>
       <c r="E25" s="18">
-        <f>Assumptions!$C$16</f>
+        <f>Assumptions!$C$41*1.0</f>
         <v/>
       </c>
       <c r="F25" s="18">
-        <f>Assumptions!$C$16</f>
+        <f>Assumptions!$C$41*1.0</f>
         <v/>
       </c>
     </row>
@@ -5861,7 +6372,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>FY26E</t>
+          <t>H2-26E</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -5892,23 +6403,23 @@
         </is>
       </c>
       <c r="B29" s="17">
-        <f>B21*Assumptions!$C$9</f>
+        <f>B21*Assumptions!$C$28</f>
         <v/>
       </c>
       <c r="C29" s="17">
-        <f>C21*Assumptions!$D$9</f>
+        <f>C21*Assumptions!$D$28</f>
         <v/>
       </c>
       <c r="D29" s="17">
-        <f>D21*Assumptions!$E$9</f>
+        <f>D21*Assumptions!$E$28</f>
         <v/>
       </c>
       <c r="E29" s="17">
-        <f>E21*Assumptions!$F$9</f>
+        <f>E21*Assumptions!$F$28</f>
         <v/>
       </c>
       <c r="F29" s="17">
-        <f>F21*Assumptions!$G$9</f>
+        <f>F21*Assumptions!$G$28</f>
         <v/>
       </c>
     </row>
@@ -5919,23 +6430,23 @@
         </is>
       </c>
       <c r="B30" s="17">
-        <f>B22*Assumptions!$C$11</f>
+        <f>B22*Assumptions!$C$31</f>
         <v/>
       </c>
       <c r="C30" s="17">
-        <f>C22*Assumptions!$D$11</f>
+        <f>C22*Assumptions!$D$31</f>
         <v/>
       </c>
       <c r="D30" s="17">
-        <f>D22*Assumptions!$E$11</f>
+        <f>D22*Assumptions!$E$31</f>
         <v/>
       </c>
       <c r="E30" s="17">
-        <f>E22*Assumptions!$F$11</f>
+        <f>E22*Assumptions!$F$31</f>
         <v/>
       </c>
       <c r="F30" s="17">
-        <f>F22*Assumptions!$G$11</f>
+        <f>F22*Assumptions!$G$31</f>
         <v/>
       </c>
     </row>
@@ -5946,23 +6457,23 @@
         </is>
       </c>
       <c r="B31" s="17">
-        <f>B23*Assumptions!$C$13</f>
+        <f>B23*Assumptions!$C$34</f>
         <v/>
       </c>
       <c r="C31" s="17">
-        <f>C23*Assumptions!$D$13</f>
+        <f>C23*Assumptions!$D$34</f>
         <v/>
       </c>
       <c r="D31" s="17">
-        <f>D23*Assumptions!$E$13</f>
+        <f>D23*Assumptions!$E$34</f>
         <v/>
       </c>
       <c r="E31" s="17">
-        <f>E23*Assumptions!$F$13</f>
+        <f>E23*Assumptions!$F$34</f>
         <v/>
       </c>
       <c r="F31" s="17">
-        <f>F23*Assumptions!$G$13</f>
+        <f>F23*Assumptions!$G$34</f>
         <v/>
       </c>
     </row>
@@ -5973,50 +6484,50 @@
         </is>
       </c>
       <c r="B32" s="17">
-        <f>B24*Assumptions!$C$15</f>
+        <f>B24*Assumptions!$C$37</f>
         <v/>
       </c>
       <c r="C32" s="17">
-        <f>C24*Assumptions!$D$15</f>
+        <f>C24*Assumptions!$D$37</f>
         <v/>
       </c>
       <c r="D32" s="17">
-        <f>D24*Assumptions!$E$15</f>
+        <f>D24*Assumptions!$E$37</f>
         <v/>
       </c>
       <c r="E32" s="17">
-        <f>E24*Assumptions!$F$15</f>
+        <f>E24*Assumptions!$F$37</f>
         <v/>
       </c>
       <c r="F32" s="17">
-        <f>F24*Assumptions!$G$15</f>
+        <f>F24*Assumptions!$G$37</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Others (half-year in the stub)</t>
         </is>
       </c>
       <c r="B33" s="18">
-        <f>Assumptions!$C$17</f>
+        <f>Assumptions!$C$42*0.5</f>
         <v/>
       </c>
       <c r="C33" s="18">
-        <f>Assumptions!$C$17</f>
+        <f>Assumptions!$C$42*1.0</f>
         <v/>
       </c>
       <c r="D33" s="18">
-        <f>Assumptions!$C$17</f>
+        <f>Assumptions!$C$42*1.0</f>
         <v/>
       </c>
       <c r="E33" s="18">
-        <f>Assumptions!$C$17</f>
+        <f>Assumptions!$C$42*1.0</f>
         <v/>
       </c>
       <c r="F33" s="18">
-        <f>Assumptions!$C$17</f>
+        <f>Assumptions!$C$42*1.0</f>
         <v/>
       </c>
     </row>
@@ -6113,14 +6624,14 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Peer figures are cross-checks from the peers' own releases (pasted, labelled); every implied value is a formula</t>
+          <t>One attributable-earnings basis throughout; the EV/EBITDA leg is a labelled, unanchored cross-check and is NOT averaged into the lens</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Relative multiples</t>
+          <t>Relative multiples (P/E leg = the lens)</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -6132,11 +6643,11 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>FY2026E attributable profit (AED mn)</t>
+          <t>FY2026E attributable profit = H1 actual + H2 model</t>
         </is>
       </c>
       <c r="C5" s="18">
-        <f>'Income Statement'!E17</f>
+        <f>Assumptions!$C$21+'Income Statement'!F17</f>
         <v/>
       </c>
     </row>
@@ -6147,52 +6658,41 @@
         </is>
       </c>
       <c r="C6" s="10">
-        <f>Assumptions!$C$51*C5/Assumptions!$C$5</f>
+        <f>Assumptions!$C$75*C5/Assumptions!$C$5</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>FY2026E EBITDA (AED mn)</t>
+          <t>FY2026E EBITDA (H1 adjusted-EBITDA + H2 model)</t>
         </is>
       </c>
       <c r="C7" s="18">
-        <f>DCF!B13</f>
+        <f>Assumptions!$C$22+DCF!B13</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA → EV</t>
-        </is>
-      </c>
-      <c r="C8" s="17">
-        <f>Assumptions!$C$52*C7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>→ equity per share through the same bridge</t>
-        </is>
-      </c>
-      <c r="C9" s="10">
-        <f>(C8+Assumptions!$C$42-Assumptions!$C$43-Assumptions!$C$44+Assumptions!$C$45+Assumptions!$C$46-Assumptions!$C$47)/Assumptions!$C$5</f>
+          <t>EV/EBITDA cross-check (house multiple, unanchored — labelled)</t>
+        </is>
+      </c>
+      <c r="C8" s="10">
+        <f>(Assumptions!$C$76*C7+Assumptions!$C$8-Assumptions!$C$10-Assumptions!$C$11+Assumptions!$C$12+Assumptions!$C$13-MAX(Assumptions!$C$14,0.02*(Assumptions!$C$76*C7+Assumptions!$C$8-Assumptions!$C$10-Assumptions!$C$11+Assumptions!$C$12+Assumptions!$C$13-Assumptions!$C$14)))/Assumptions!$C$5</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Relative lens (mean of the two)</t>
+          <t>Relative lens (P/E leg)</t>
         </is>
       </c>
       <c r="B11" s="15" t="n"/>
       <c r="C11" s="13">
-        <f>AVERAGE(C6,C9)</f>
+        <f>C6</f>
         <v/>
       </c>
       <c r="D11" s="15" t="n"/>
@@ -6203,22 +6703,22 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>bear / bull (blended lens scaled to the 4.08x floor · 9.5x ceiling)</t>
+          <t>bear / bull (lens scaled to the peer-set floor 4.73x and ceiling 8.10x)</t>
         </is>
       </c>
       <c r="C12" s="10">
-        <f>C11*4.08/Assumptions!$C$51</f>
+        <f>C11*4.73/Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="D12" s="10">
-        <f>C11*9.5/Assumptions!$C$51</f>
+        <f>C11*8.1/Assumptions!$C$75</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Trailing cross-checks (formulas on disclosed figures)</t>
+          <t>Trailing cross-checks</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -6230,78 +6730,89 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Trailing P/E on FY2025 profit</t>
+          <t>Trailing P/E on FY2025 attributable profit</t>
         </is>
       </c>
       <c r="C15" s="28">
-        <f>DCF!C27/3925.705</f>
+        <f>DCF!C33/Assumptions!$C$71</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Trailing EV/EBITDA (EV = mktcap + net debt)</t>
+          <t>Trailing P/E on FY2025 group profit (dual-framed)</t>
         </is>
       </c>
       <c r="C16" s="28">
-        <f>(DCF!C27+Assumptions!$C$43-Assumptions!$C$42)/4895.552000000001</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+        <f>DCF!C33/Assumptions!$C$70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Trailing EV/EBITDA (mktcap + FY2025 strict net debt over house EBITDA)</t>
+        </is>
+      </c>
+      <c r="C17" s="28">
+        <f>(DCF!C33+Assumptions!$C$73)/Assumptions!$C$72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Normalised earnings power</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Through-cycle development sales → recognised revenue (85%)</t>
-        </is>
-      </c>
-      <c r="C19" s="17">
-        <f>Assumptions!$C$53*0.85+(654.658+791.771+5008.749)*1.15</f>
-        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Through-cycle net margin</t>
-        </is>
-      </c>
-      <c r="C20" s="9">
-        <f>Assumptions!$C$54</f>
+          <t>Through-cycle revenue = 85% × cycle sales + recurring legs × 1.15</t>
+        </is>
+      </c>
+      <c r="C20" s="17">
+        <f>Assumptions!$C$77*0.85+Assumptions!$C$79*1.15</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Normalised net profit</t>
-        </is>
-      </c>
-      <c r="C21" s="17">
-        <f>C19*C20</f>
+          <t>Through-cycle net margin</t>
+        </is>
+      </c>
+      <c r="C21" s="9">
+        <f>Assumptions!$C$78</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
+          <t>Normalised net profit</t>
+        </is>
+      </c>
+      <c r="C22" s="17">
+        <f>C20*C21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
           <t>Normalised EPS</t>
         </is>
       </c>
-      <c r="C22" s="10">
-        <f>C21/Assumptions!$C$5</f>
+      <c r="C23" s="10">
+        <f>C22/Assumptions!$C$5</f>
         <v/>
       </c>
     </row>
@@ -6312,22 +6823,22 @@
         </is>
       </c>
       <c r="C28" s="23">
-        <f>C22*Assumptions!$C$55</f>
+        <f>C23*Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="E28" s="10">
-        <f>C22*6</f>
+        <f>C23*6</f>
         <v/>
       </c>
       <c r="F28" s="10">
-        <f>C22*10.5</f>
+        <f>C23*10.5</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Book value &amp; sustainable return</t>
+          <t>Book value &amp; sustainable return (rolled to the anchor like the DCF)</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -6339,11 +6850,11 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Book value per share (audited FY2025 attributable equity)</t>
+          <t>Book value per share (30-Jun-2026 attributable equity)</t>
         </is>
       </c>
       <c r="C31" s="10">
-        <f>Assumptions!$C$48/Assumptions!$C$5</f>
+        <f>Assumptions!$C$15/Assumptions!$C$5</f>
         <v/>
       </c>
     </row>
@@ -6354,26 +6865,26 @@
         </is>
       </c>
       <c r="C32" s="28">
-        <f>(Assumptions!$C$56-Assumptions!$C$38)/(DCF!C24-Assumptions!$C$38)</f>
+        <f>(Assumptions!$C$81-Assumptions!$C$66)/(DCF!C30-Assumptions!$C$66)</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="22" t="inlineStr">
         <is>
-          <t>Book lens = BVPS × justified P/B</t>
+          <t>Book lens = BVPS × justified P/B × anchor roll</t>
         </is>
       </c>
       <c r="C36" s="23">
-        <f>C31*C32</f>
+        <f>C31*C32*DCF!C61</f>
         <v/>
       </c>
       <c r="E36" s="10">
-        <f>C31*((0.055-Assumptions!$C$38)/(DCF!C24-Assumptions!$C$38))</f>
+        <f>C31*((0.055-Assumptions!$C$66)/(DCF!C30-Assumptions!$C$66))*DCF!C61</f>
         <v/>
       </c>
       <c r="F36" s="10">
-        <f>C31*((0.095-Assumptions!$C$38)/(DCF!C24-Assumptions!$C$38))</f>
+        <f>C31*((0.095-Assumptions!$C$66)/(DCF!C30-Assumptions!$C$66))*DCF!C61</f>
         <v/>
       </c>
     </row>
@@ -6388,7 +6899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -6404,7 +6915,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DCF — waterfall, cost of capital build, terminal block, bridge to per-share</t>
+          <t>DCF — waterfall, working-capital components, cost of capital, terminal block, bridge</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6418,7 +6929,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Chains live off Segments and Assumptions; the three engine alternatives are labelled pastes</t>
+          <t>Valuation date 30-Jun-2026; H2-2026 stub then annual; every chain live</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6941,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>FY26E</t>
+          <t>H2-26E</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -6515,23 +7026,23 @@
         </is>
       </c>
       <c r="B7" s="17">
-        <f>-Assumptions!$C$18*B5</f>
+        <f>-Assumptions!$C$43*B5</f>
         <v/>
       </c>
       <c r="C7" s="17">
-        <f>-Assumptions!$D$18*C5</f>
+        <f>-Assumptions!$D$43*C5</f>
         <v/>
       </c>
       <c r="D7" s="17">
-        <f>-Assumptions!$E$18*D5</f>
+        <f>-Assumptions!$E$43*D5</f>
         <v/>
       </c>
       <c r="E7" s="17">
-        <f>-Assumptions!$F$18*E5</f>
+        <f>-Assumptions!$F$43*E5</f>
         <v/>
       </c>
       <c r="F7" s="17">
-        <f>-Assumptions!$G$18*F5</f>
+        <f>-Assumptions!$G$43*F5</f>
         <v/>
       </c>
     </row>
@@ -6542,23 +7053,23 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>-Assumptions!$C$19*B5</f>
+        <f>-Assumptions!$C$44*B5</f>
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>-Assumptions!$D$19*C5</f>
+        <f>-Assumptions!$D$44*C5</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>-Assumptions!$E$19*D5</f>
+        <f>-Assumptions!$E$44*D5</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>-Assumptions!$F$19*E5</f>
+        <f>-Assumptions!$F$44*E5</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>-Assumptions!$G$19*F5</f>
+        <f>-Assumptions!$G$44*F5</f>
         <v/>
       </c>
     </row>
@@ -6569,23 +7080,23 @@
         </is>
       </c>
       <c r="B9" s="18">
-        <f>Assumptions!$C$20</f>
+        <f>Assumptions!$C$45</f>
         <v/>
       </c>
       <c r="C9" s="18">
-        <f>Assumptions!$D$20</f>
+        <f>Assumptions!$D$45</f>
         <v/>
       </c>
       <c r="D9" s="18">
-        <f>Assumptions!$E$20</f>
+        <f>Assumptions!$E$45</f>
         <v/>
       </c>
       <c r="E9" s="18">
-        <f>Assumptions!$F$20</f>
+        <f>Assumptions!$F$45</f>
         <v/>
       </c>
       <c r="F9" s="18">
-        <f>Assumptions!$G$20</f>
+        <f>Assumptions!$G$45</f>
         <v/>
       </c>
     </row>
@@ -6646,27 +7157,27 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Depreciation &amp; amortisation</t>
+          <t>Depreciation &amp; amortisation (asset-base)</t>
         </is>
       </c>
       <c r="B12" s="17">
-        <f>Assumptions!$C$21*B5</f>
+        <f>Assumptions!$C$46*(B21+Assumptions!$C$47/2)*0.5</f>
         <v/>
       </c>
       <c r="C12" s="17">
-        <f>Assumptions!$C$21*C5</f>
+        <f>Assumptions!$C$46*(C21+Assumptions!$D$47/2)*1.0</f>
         <v/>
       </c>
       <c r="D12" s="17">
-        <f>Assumptions!$C$21*D5</f>
+        <f>Assumptions!$C$46*(D21+Assumptions!$E$47/2)*1.0</f>
         <v/>
       </c>
       <c r="E12" s="17">
-        <f>Assumptions!$C$21*E5</f>
+        <f>Assumptions!$C$46*(E21+Assumptions!$F$47/2)*1.0</f>
         <v/>
       </c>
       <c r="F12" s="17">
-        <f>Assumptions!$C$21*F5</f>
+        <f>Assumptions!$C$46*(F21+Assumptions!$G$47/2)*1.0</f>
         <v/>
       </c>
     </row>
@@ -6704,23 +7215,23 @@
         </is>
       </c>
       <c r="B14" s="17">
-        <f>B10*(1-Assumptions!$C$24)</f>
+        <f>B10*(1-Assumptions!$C$48)</f>
         <v/>
       </c>
       <c r="C14" s="17">
-        <f>C10*(1-Assumptions!$C$24)</f>
+        <f>C10*(1-Assumptions!$C$48)</f>
         <v/>
       </c>
       <c r="D14" s="17">
-        <f>D10*(1-Assumptions!$C$24)</f>
+        <f>D10*(1-Assumptions!$C$48)</f>
         <v/>
       </c>
       <c r="E14" s="17">
-        <f>E10*(1-Assumptions!$C$24)</f>
+        <f>E10*(1-Assumptions!$C$48)</f>
         <v/>
       </c>
       <c r="F14" s="17">
-        <f>F10*(1-Assumptions!$C$24)</f>
+        <f>F10*(1-Assumptions!$C$48)</f>
         <v/>
       </c>
     </row>
@@ -6758,50 +7269,50 @@
         </is>
       </c>
       <c r="B16" s="17">
-        <f>-Assumptions!$C$22</f>
+        <f>-Assumptions!$C$47</f>
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>-Assumptions!$D$22</f>
+        <f>-Assumptions!$D$47</f>
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>-Assumptions!$E$22</f>
+        <f>-Assumptions!$E$47</f>
         <v/>
       </c>
       <c r="E16" s="17">
-        <f>-Assumptions!$F$22</f>
+        <f>-Assumptions!$F$47</f>
         <v/>
       </c>
       <c r="F16" s="17">
-        <f>-Assumptions!$G$22</f>
+        <f>-Assumptions!$G$47</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>− Δ working capital (release enters +)</t>
-        </is>
-      </c>
-      <c r="B17" s="18">
-        <f>Assumptions!$C$23</f>
-        <v/>
-      </c>
-      <c r="C17" s="18">
-        <f>Assumptions!$D$23</f>
-        <v/>
-      </c>
-      <c r="D17" s="18">
-        <f>Assumptions!$E$23</f>
-        <v/>
-      </c>
-      <c r="E17" s="18">
-        <f>Assumptions!$F$23</f>
-        <v/>
-      </c>
-      <c r="F17" s="18">
-        <f>Assumptions!$G$23</f>
+          <t>− Δ working capital (from components below)</t>
+        </is>
+      </c>
+      <c r="B17" s="17">
+        <f>-B26</f>
+        <v/>
+      </c>
+      <c r="C17" s="17">
+        <f>-C26</f>
+        <v/>
+      </c>
+      <c r="D17" s="17">
+        <f>-D26</f>
+        <v/>
+      </c>
+      <c r="E17" s="17">
+        <f>-E26</f>
+        <v/>
+      </c>
+      <c r="F17" s="17">
+        <f>-F26</f>
         <v/>
       </c>
     </row>
@@ -6835,27 +7346,27 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Discount factor</t>
+          <t>Discount factor (period-end from 30-Jun-2026)</t>
         </is>
       </c>
       <c r="B19" s="29">
-        <f>1/(1+$C$30)^1</f>
+        <f>1/(1+$C$36)^0.5</f>
         <v/>
       </c>
       <c r="C19" s="29">
-        <f>1/(1+$C$30)^2</f>
+        <f>1/(1+$C$36)^1.5</f>
         <v/>
       </c>
       <c r="D19" s="29">
-        <f>1/(1+$C$30)^3</f>
+        <f>1/(1+$C$36)^2.5</f>
         <v/>
       </c>
       <c r="E19" s="29">
-        <f>1/(1+$C$30)^4</f>
+        <f>1/(1+$C$36)^3.5</f>
         <v/>
       </c>
       <c r="F19" s="29">
-        <f>1/(1+$C$30)^5</f>
+        <f>1/(1+$C$36)^4.5</f>
         <v/>
       </c>
     </row>
@@ -6886,370 +7397,553 @@
         <v/>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Depreciable asset base (opening)</t>
+        </is>
+      </c>
+      <c r="B21" s="18">
+        <f>Assumptions!$C$23</f>
+        <v/>
+      </c>
+      <c r="C21" s="17">
+        <f>B21+Assumptions!$C$47-B12</f>
+        <v/>
+      </c>
+      <c r="D21" s="17">
+        <f>C21+Assumptions!$D$47-C12</f>
+        <v/>
+      </c>
+      <c r="E21" s="17">
+        <f>D21+Assumptions!$E$47-D12</f>
+        <v/>
+      </c>
+      <c r="F21" s="17">
+        <f>E21+Assumptions!$F$47-E12</f>
+        <v/>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Cost of capital — built on the sheet, never pasted</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="15" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="15" t="n"/>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="15" t="n"/>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Receivables (days × revenue)</t>
+        </is>
+      </c>
+      <c r="B22" s="17">
+        <f>Assumptions!$C$55/365*(Assumptions!$C$19+B5)</f>
+        <v/>
+      </c>
+      <c r="C22" s="17">
+        <f>Assumptions!$D$55/365*C5</f>
+        <v/>
+      </c>
+      <c r="D22" s="17">
+        <f>Assumptions!$E$55/365*D5</f>
+        <v/>
+      </c>
+      <c r="E22" s="17">
+        <f>Assumptions!$F$55/365*E5</f>
+        <v/>
+      </c>
+      <c r="F22" s="17">
+        <f>Assumptions!$G$55/365*F5</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Normalised risk-free rate rf* = AED yield − sovereign spread</t>
-        </is>
-      </c>
-      <c r="C23" s="20">
-        <f>Assumptions!$C$31-Assumptions!$C$32</f>
+          <t>Inventories + WIP (roll)</t>
+        </is>
+      </c>
+      <c r="B23" s="17">
+        <f>Assumptions!$C$17+Assumptions!$C$56*Assumptions!$C$26-Assumptions!$C$57*Segments!B18*(1-Assumptions!$C$28)</f>
+        <v/>
+      </c>
+      <c r="C23" s="17">
+        <f>B23+Assumptions!$C$56*Assumptions!$D$26-Assumptions!$C$57*Segments!C18*(1-Assumptions!$D$28)</f>
+        <v/>
+      </c>
+      <c r="D23" s="17">
+        <f>C23+Assumptions!$C$56*Assumptions!$E$26-Assumptions!$C$57*Segments!D18*(1-Assumptions!$E$28)</f>
+        <v/>
+      </c>
+      <c r="E23" s="17">
+        <f>D23+Assumptions!$C$56*Assumptions!$F$26-Assumptions!$C$57*Segments!E18*(1-Assumptions!$F$28)</f>
+        <v/>
+      </c>
+      <c r="F23" s="17">
+        <f>E23+Assumptions!$C$56*Assumptions!$G$26-Assumptions!$C$57*Segments!F18*(1-Assumptions!$G$28)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Cost of equity Ke = rf* + β × ERP</t>
-        </is>
-      </c>
-      <c r="C24" s="30">
-        <f>C23+Assumptions!$C$34*Assumptions!$C$33</f>
+          <t>Payables + advances (cover × costs)</t>
+        </is>
+      </c>
+      <c r="B24" s="17">
+        <f>Assumptions!$C$58*(Assumptions!$C$19+B5-Assumptions!$C$20-B6)</f>
+        <v/>
+      </c>
+      <c r="C24" s="17">
+        <f>Assumptions!$D$58*(C5-C6)</f>
+        <v/>
+      </c>
+      <c r="D24" s="17">
+        <f>Assumptions!$E$58*(D5-D6)</f>
+        <v/>
+      </c>
+      <c r="E24" s="17">
+        <f>Assumptions!$F$58*(E5-E6)</f>
+        <v/>
+      </c>
+      <c r="F24" s="17">
+        <f>Assumptions!$G$58*(F5-F6)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Marginal cost of debt Kd = 6M EIBOR + margin</t>
-        </is>
-      </c>
-      <c r="C25" s="30">
-        <f>Assumptions!$C$35+Assumptions!$C$36</f>
+          <t>Net working capital</t>
+        </is>
+      </c>
+      <c r="B25" s="17">
+        <f>B22+B23-B24</f>
+        <v/>
+      </c>
+      <c r="C25" s="17">
+        <f>C22+C23-C24</f>
+        <v/>
+      </c>
+      <c r="D25" s="17">
+        <f>D22+D23-D24</f>
+        <v/>
+      </c>
+      <c r="E25" s="17">
+        <f>E22+E23-E24</f>
+        <v/>
+      </c>
+      <c r="F25" s="17">
+        <f>F22+F23-F24</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Kd after tax</t>
-        </is>
-      </c>
-      <c r="C26" s="30">
-        <f>C25*(1-Assumptions!$C$24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Market capitalisation (spot × shares)</t>
-        </is>
-      </c>
-      <c r="C27" s="17">
-        <f>Assumptions!$C$4*Assumptions!$C$5</f>
+          <t>Δ working capital</t>
+        </is>
+      </c>
+      <c r="B26" s="17">
+        <f>B25-(Assumptions!$C$16+Assumptions!$C$17-Assumptions!$C$18)</f>
+        <v/>
+      </c>
+      <c r="C26" s="17">
+        <f>C25-B25</f>
+        <v/>
+      </c>
+      <c r="D26" s="17">
+        <f>D25-C25</f>
+        <v/>
+      </c>
+      <c r="E26" s="17">
+        <f>E25-D25</f>
+        <v/>
+      </c>
+      <c r="F26" s="17">
+        <f>F25-E25</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Equity weight  E/(E+D)</t>
-        </is>
-      </c>
-      <c r="C28" s="30">
-        <f>C27/(C27+Assumptions!$C$43)</f>
-        <v/>
-      </c>
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Cost of capital — built on the sheet</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="15" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
+      <c r="H28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Debt weight  D/(E+D), book debt at market</t>
-        </is>
-      </c>
-      <c r="C29" s="30">
-        <f>1-C28</f>
+          <t>Normalised risk-free rate rf* = AED yield − sovereign spread</t>
+        </is>
+      </c>
+      <c r="C29" s="20">
+        <f>Assumptions!$C$60-Assumptions!$C$61</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Cost of capital (explicit window)</t>
-        </is>
-      </c>
-      <c r="C30" s="31">
-        <f>C28*C24+C29*C26</f>
+          <t>Cost of equity Ke = rf* + β × ERP (β from the panel-proxy regression)</t>
+        </is>
+      </c>
+      <c r="C30" s="30">
+        <f>C29+Assumptions!$C$63*Assumptions!$C$62</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Terminal cost of capital (terminal weights)</t>
-        </is>
-      </c>
-      <c r="C31" s="31">
-        <f>(1-Assumptions!$C$37)*C24+Assumptions!$C$37*C25*(1-Assumptions!$C$24)</f>
+          <t>Marginal cost of debt Kd = 6M EIBOR + margin</t>
+        </is>
+      </c>
+      <c r="C31" s="30">
+        <f>Assumptions!$C$64+Assumptions!$C$65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Kd after tax</t>
+        </is>
+      </c>
+      <c r="C32" s="30">
+        <f>C31*(1-Assumptions!$C$48)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>Terminal block — reinvestment derived, never typed</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="n"/>
-      <c r="C33" s="15" t="n"/>
-      <c r="D33" s="15" t="n"/>
-      <c r="E33" s="15" t="n"/>
-      <c r="F33" s="15" t="n"/>
-      <c r="G33" s="15" t="n"/>
-      <c r="H33" s="15" t="n"/>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Market capitalisation (spot × shares)</t>
+        </is>
+      </c>
+      <c r="C33" s="17">
+        <f>Assumptions!$C$4*Assumptions!$C$5</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth g</t>
-        </is>
-      </c>
-      <c r="C34" s="20">
-        <f>Assumptions!$C$38</f>
+          <t>Equity weight E/(E+D), debt at the 30-Jun-2026 book</t>
+        </is>
+      </c>
+      <c r="C34" s="30">
+        <f>C33/(C33+Assumptions!$C$10)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital</t>
-        </is>
-      </c>
-      <c r="C35" s="20">
-        <f>Assumptions!$C$39</f>
+          <t>Debt weight D/(E+D)</t>
+        </is>
+      </c>
+      <c r="C35" s="30">
+        <f>1-C34</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Reinvestment rate = g / ROIC</t>
-        </is>
-      </c>
-      <c r="C36" s="30">
-        <f>C34/C35</f>
+          <t>Cost of capital (explicit window)</t>
+        </is>
+      </c>
+      <c r="C36" s="31">
+        <f>C34*C30+C35*C32</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Terminal NOPAT = FY2030E NOPAT × (1+g)</t>
-        </is>
-      </c>
-      <c r="C37" s="17">
-        <f>F14*(1+C34)</f>
+          <t>Terminal debt weight — DERIVED from the FY2030E balance sheet</t>
+        </is>
+      </c>
+      <c r="C37" s="30">
+        <f>'Balance Sheet'!J12/('Balance Sheet'!J12+'Balance Sheet'!J14+'Balance Sheet'!J15)</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Terminal value = NOPAT × (1−RR) / (WACCterm − g)</t>
-        </is>
-      </c>
-      <c r="C38" s="17">
-        <f>C37*(1-C36)/(C31-C34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>PV of terminal value (year-5 factor)</t>
-        </is>
-      </c>
-      <c r="C39" s="17">
-        <f>C38*F19</f>
+          <t>Terminal cost of capital (derived weights)</t>
+        </is>
+      </c>
+      <c r="C38" s="31">
+        <f>(1-C37)*C30+C37*C31*(1-Assumptions!$C$48)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>PV of explicit years</t>
-        </is>
-      </c>
-      <c r="C40" s="17">
-        <f>SUM(B20:F20)</f>
-        <v/>
-      </c>
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Terminal block — reinvestment derived</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="15" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="15" t="n"/>
+      <c r="H40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Enterprise value</t>
-        </is>
-      </c>
-      <c r="C41" s="27">
-        <f>C39+C40</f>
+          <t>Terminal growth g</t>
+        </is>
+      </c>
+      <c r="C41" s="20">
+        <f>Assumptions!$C$66</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Terminal value share of enterprise value</t>
-        </is>
-      </c>
-      <c r="C42" s="32">
-        <f>C39/C41</f>
+          <t>Terminal return on invested capital</t>
+        </is>
+      </c>
+      <c r="C42" s="20">
+        <f>Assumptions!$C$67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Reinvestment rate = g / ROIC</t>
+        </is>
+      </c>
+      <c r="C43" s="30">
+        <f>C41/C42</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>EV → equity bridge (31-Dec-2025, audited anchors)</t>
-        </is>
-      </c>
-      <c r="B44" s="15" t="n"/>
-      <c r="C44" s="15" t="n"/>
-      <c r="D44" s="15" t="n"/>
-      <c r="E44" s="15" t="n"/>
-      <c r="F44" s="15" t="n"/>
-      <c r="G44" s="15" t="n"/>
-      <c r="H44" s="15" t="n"/>
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Terminal NOPAT = FY2030E NOPAT × (1+g)</t>
+        </is>
+      </c>
+      <c r="C44" s="17">
+        <f>F14*(1+C41)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>+ Cash and bank balances</t>
-        </is>
-      </c>
-      <c r="C45" s="18">
-        <f>Assumptions!$C$42</f>
+          <t>Terminal value = NOPAT × (1−RR) / (WACCterm − g)</t>
+        </is>
+      </c>
+      <c r="C45" s="17">
+        <f>C44*(1-C43)/(C38-C41)</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>− Gross debt incl. related-party loan</t>
-        </is>
-      </c>
-      <c r="C46" s="18">
-        <f>-Assumptions!$C$43</f>
+          <t>PV of terminal value (year-4.5 factor)</t>
+        </is>
+      </c>
+      <c r="C46" s="17">
+        <f>C45*F19</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>− Lease liabilities</t>
-        </is>
-      </c>
-      <c r="C47" s="18">
-        <f>-Assumptions!$C$44</f>
+          <t>PV of explicit periods</t>
+        </is>
+      </c>
+      <c r="C47" s="17">
+        <f>SUM(B20:F20)</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>+ Associates &amp; JVs at carrying value</t>
-        </is>
-      </c>
-      <c r="C48" s="18">
-        <f>Assumptions!$C$45</f>
+          <t>Enterprise value</t>
+        </is>
+      </c>
+      <c r="C48" s="27">
+        <f>C46+C47</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>+ Investments in financial assets</t>
-        </is>
-      </c>
-      <c r="C49" s="18">
-        <f>Assumptions!$C$46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>− Non-controlling interests (book)</t>
-        </is>
-      </c>
-      <c r="C50" s="18">
-        <f>-Assumptions!$C$47</f>
+          <t>Terminal value share of enterprise value</t>
+        </is>
+      </c>
+      <c r="C49" s="32">
+        <f>C46/C48</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Equity value attributable (31-Dec-2025)</t>
-        </is>
-      </c>
-      <c r="C51" s="27">
-        <f>C41+SUM(C45:C50)</f>
-        <v/>
-      </c>
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>EV → equity bridge (30-Jun-2026, available-cash basis)</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="n"/>
+      <c r="C51" s="15" t="n"/>
+      <c r="D51" s="15" t="n"/>
+      <c r="E51" s="15" t="n"/>
+      <c r="F51" s="15" t="n"/>
+      <c r="G51" s="15" t="n"/>
+      <c r="H51" s="15" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Fair value per share at 31-Dec-2025</t>
-        </is>
-      </c>
-      <c r="C52" s="23">
-        <f>C51/Assumptions!$C$5</f>
+          <t>+ Unrestricted (available) cash — disclosed</t>
+        </is>
+      </c>
+      <c r="C52" s="18">
+        <f>Assumptions!$C$8</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Anchor accretion factor (1+Ke)^(days/365)</t>
-        </is>
-      </c>
-      <c r="C53" s="29">
-        <f>(1+C24)^(Assumptions!$C$40/365)</f>
-        <v/>
+          <t xml:space="preserve">   (project escrow/restricted cash of 3,703 is excluded: it funds completion of the backlog the DCF values)</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>Fair value per share at the 7-Aug-2026 anchor</t>
-        </is>
-      </c>
-      <c r="C54" s="23">
-        <f>C52*C53</f>
+          <t>− Gross debt incl. related-party loan</t>
+        </is>
+      </c>
+      <c r="C54" s="18">
+        <f>-Assumptions!$C$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>− Lease liabilities</t>
+        </is>
+      </c>
+      <c r="C55" s="18">
+        <f>-Assumptions!$C$11</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Scenario re-runs (engine outputs, pasted): backlog run-off / growth-hold / Egypt stress</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="n">
-        <v>4.179391161327742</v>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>7.393430194946205</v>
-      </c>
-      <c r="E56" s="7" t="n">
-        <v>5.086676693032556</v>
+          <t>+ Associates &amp; JVs at carrying value</t>
+        </is>
+      </c>
+      <c r="C56" s="18">
+        <f>Assumptions!$C$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>+ Investments in financial assets</t>
+        </is>
+      </c>
+      <c r="C57" s="18">
+        <f>Assumptions!$C$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>− Non-controlling interests, capitalised at share of equity value (MAX of book and 2%)</t>
+        </is>
+      </c>
+      <c r="C58" s="17">
+        <f>-MAX(Assumptions!$C$14,0.02*(C48+C52-Assumptions!$C$10-Assumptions!$C$11+Assumptions!$C$12+Assumptions!$C$13-Assumptions!$C$14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Equity value attributable (30-Jun-2026)</t>
+        </is>
+      </c>
+      <c r="C59" s="27">
+        <f>C48+SUM(C52:C58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Fair value per share at 30-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C60" s="23">
+        <f>C59/Assumptions!$C$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Anchor accretion (1+Ke)^(38/365)</t>
+        </is>
+      </c>
+      <c r="C61" s="29">
+        <f>(1+C30)^(Assumptions!$C$68/365)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Fair value per share at the 7-Aug-2026 anchor</t>
+        </is>
+      </c>
+      <c r="C62" s="23">
+        <f>C60*C61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Alternatives (engine re-runs, pasted; driver vectors on Assumptions): run-off stress / growth-hold / Egypt stress / gross-cash basis</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>3.784078327184524</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>6.305618176058718</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>4.311736370448707</v>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>5.520395478237414</v>
       </c>
     </row>
   </sheetData>
@@ -7263,25 +7957,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Income statement — 3 years audited + 5 years forecast</t>
+          <t>Income statement — 3 years audited + H1-2026 actual + forecast</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7293,11 +7988,12 @@
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>FY2023 is the Q Holding perimeter; FY2024 contains the AED 9,192mn bargain-purchase gain (dual-framed)</t>
+          <t>FY2023 is the Q Holding perimeter; FY2024 contains the AED 9,192mn bargain gain (dual-framed); column E is the H1-2026 actual; forecast runs H2-2026E..FY2030E</t>
         </is>
       </c>
     </row>
@@ -7320,25 +8016,30 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>FY26E</t>
+          <t>H1-26A</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
+          <t>H2-26E</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
           <t>FY27E</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>FY28E</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>FY29E</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>FY30E</t>
         </is>
@@ -7359,23 +8060,26 @@
       <c r="D5" s="19" t="n">
         <v>13828.869</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="19" t="n">
+        <v>9188.304</v>
+      </c>
+      <c r="F5" s="18">
         <f>DCF!B5</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="G5" s="18">
         <f>DCF!C5</f>
         <v/>
       </c>
-      <c r="G5" s="18">
+      <c r="H5" s="18">
         <f>DCF!D5</f>
         <v/>
       </c>
-      <c r="H5" s="18">
+      <c r="I5" s="18">
         <f>DCF!E5</f>
         <v/>
       </c>
-      <c r="I5" s="18">
+      <c r="J5" s="18">
         <f>DCF!F5</f>
         <v/>
       </c>
@@ -7395,23 +8099,26 @@
       <c r="D6" s="19" t="n">
         <v>5025.259</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="19" t="n">
+        <v>3201.275</v>
+      </c>
+      <c r="F6" s="18">
         <f>DCF!B6</f>
         <v/>
       </c>
-      <c r="F6" s="18">
+      <c r="G6" s="18">
         <f>DCF!C6</f>
         <v/>
       </c>
-      <c r="G6" s="18">
+      <c r="H6" s="18">
         <f>DCF!D6</f>
         <v/>
       </c>
-      <c r="H6" s="18">
+      <c r="I6" s="18">
         <f>DCF!E6</f>
         <v/>
       </c>
-      <c r="I6" s="18">
+      <c r="J6" s="18">
         <f>DCF!F6</f>
         <v/>
       </c>
@@ -7431,23 +8138,23 @@
       <c r="D7" s="19" t="n">
         <v>4895.552000000001</v>
       </c>
-      <c r="E7" s="18">
+      <c r="F7" s="18">
         <f>DCF!B13</f>
         <v/>
       </c>
-      <c r="F7" s="18">
+      <c r="G7" s="18">
         <f>DCF!C13</f>
         <v/>
       </c>
-      <c r="G7" s="18">
+      <c r="H7" s="18">
         <f>DCF!D13</f>
         <v/>
       </c>
-      <c r="H7" s="18">
+      <c r="I7" s="18">
         <f>DCF!E13</f>
         <v/>
       </c>
-      <c r="I7" s="18">
+      <c r="J7" s="18">
         <f>DCF!F13</f>
         <v/>
       </c>
@@ -7470,10 +8177,6 @@
         <f>D7/D5</f>
         <v/>
       </c>
-      <c r="E8" s="11">
-        <f>E7/E5</f>
-        <v/>
-      </c>
       <c r="F8" s="11">
         <f>F7/F5</f>
         <v/>
@@ -7490,6 +8193,10 @@
         <f>I7/I5</f>
         <v/>
       </c>
+      <c r="J8" s="11">
+        <f>J7/J5</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -7506,23 +8213,23 @@
       <c r="D9" s="19" t="n">
         <v>610.4829999999999</v>
       </c>
-      <c r="E9" s="18">
+      <c r="F9" s="18">
         <f>DCF!B12</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="G9" s="18">
         <f>DCF!C12</f>
         <v/>
       </c>
-      <c r="G9" s="18">
+      <c r="H9" s="18">
         <f>DCF!D12</f>
         <v/>
       </c>
-      <c r="H9" s="18">
+      <c r="I9" s="18">
         <f>DCF!E12</f>
         <v/>
       </c>
-      <c r="I9" s="18">
+      <c r="J9" s="18">
         <f>DCF!F12</f>
         <v/>
       </c>
@@ -7545,10 +8252,6 @@
         <f>D7-D9</f>
         <v/>
       </c>
-      <c r="E10" s="17">
-        <f>E7-E9</f>
-        <v/>
-      </c>
       <c r="F10" s="17">
         <f>F7-F9</f>
         <v/>
@@ -7565,6 +8268,10 @@
         <f>I7-I9</f>
         <v/>
       </c>
+      <c r="J10" s="17">
+        <f>J7-J9</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -7581,24 +8288,24 @@
       <c r="D11" s="19" t="n">
         <v>-127.466</v>
       </c>
-      <c r="E11" s="17">
-        <f>Assumptions!$C$29*'Balance Sheet'!D9-(DCF!$C$25*(Assumptions!$C$43+Assumptions!$C$28)/2+35)</f>
-        <v/>
-      </c>
       <c r="F11" s="17">
-        <f>Assumptions!$C$29*'Balance Sheet'!E9-(DCF!$C$25*(Assumptions!$C$28+Assumptions!$D$28)/2+35)</f>
+        <f>(Assumptions!$C$52*'Balance Sheet'!E9-(DCF!$C$31*(Assumptions!$C$10+Assumptions!$C$51)/2+Assumptions!$C$53))*0.5</f>
         <v/>
       </c>
       <c r="G11" s="17">
-        <f>Assumptions!$C$29*'Balance Sheet'!F9-(DCF!$C$25*(Assumptions!$D$28+Assumptions!$E$28)/2+35)</f>
+        <f>(Assumptions!$C$52*'Balance Sheet'!F9-(DCF!$C$31*(Assumptions!$C$51+Assumptions!$D$51)/2+Assumptions!$C$53))*1.0</f>
         <v/>
       </c>
       <c r="H11" s="17">
-        <f>Assumptions!$C$29*'Balance Sheet'!G9-(DCF!$C$25*(Assumptions!$E$28+Assumptions!$F$28)/2+35)</f>
+        <f>(Assumptions!$C$52*'Balance Sheet'!G9-(DCF!$C$31*(Assumptions!$D$51+Assumptions!$E$51)/2+Assumptions!$C$53))*1.0</f>
         <v/>
       </c>
       <c r="I11" s="17">
-        <f>Assumptions!$C$29*'Balance Sheet'!H9-(DCF!$C$25*(Assumptions!$F$28+Assumptions!$G$28)/2+35)</f>
+        <f>(Assumptions!$C$52*'Balance Sheet'!H9-(DCF!$C$31*(Assumptions!$E$51+Assumptions!$F$51)/2+Assumptions!$C$53))*1.0</f>
+        <v/>
+      </c>
+      <c r="J11" s="17">
+        <f>(Assumptions!$C$52*'Balance Sheet'!I9-(DCF!$C$31*(Assumptions!$F$51+Assumptions!$G$51)/2+Assumptions!$C$53))*1.0</f>
         <v/>
       </c>
     </row>
@@ -7617,24 +8324,24 @@
       <c r="D12" s="19" t="n">
         <v>263.592</v>
       </c>
-      <c r="E12" s="17">
-        <f>Assumptions!$C$26*(1+Assumptions!$C$27)^0</f>
-        <v/>
-      </c>
-      <c r="F12" s="17">
-        <f>Assumptions!$C$26*(1+Assumptions!$C$27)^1</f>
-        <v/>
-      </c>
-      <c r="G12" s="17">
-        <f>Assumptions!$C$26*(1+Assumptions!$C$27)^2</f>
-        <v/>
-      </c>
-      <c r="H12" s="17">
-        <f>Assumptions!$C$26*(1+Assumptions!$C$27)^3</f>
-        <v/>
-      </c>
-      <c r="I12" s="17">
-        <f>Assumptions!$C$26*(1+Assumptions!$C$27)^4</f>
+      <c r="F12" s="18">
+        <f>Assumptions!$C$50</f>
+        <v/>
+      </c>
+      <c r="G12" s="18">
+        <f>Assumptions!$D$50</f>
+        <v/>
+      </c>
+      <c r="H12" s="18">
+        <f>Assumptions!$E$50</f>
+        <v/>
+      </c>
+      <c r="I12" s="18">
+        <f>Assumptions!$F$50</f>
+        <v/>
+      </c>
+      <c r="J12" s="18">
+        <f>Assumptions!$G$50</f>
         <v/>
       </c>
     </row>
@@ -7656,9 +8363,8 @@
         <f>D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="17">
-        <f>E10+E11+E12</f>
-        <v/>
+      <c r="E13" s="19" t="n">
+        <v>2601.227</v>
       </c>
       <c r="F13" s="17">
         <f>F10+F11+F12</f>
@@ -7676,6 +8382,10 @@
         <f>I10+I11+I12</f>
         <v/>
       </c>
+      <c r="J13" s="17">
+        <f>J10+J11+J12</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -7692,24 +8402,27 @@
       <c r="D14" s="19" t="n">
         <v>-495.49</v>
       </c>
-      <c r="E14" s="17">
-        <f>-E13*Assumptions!$C$24</f>
-        <v/>
+      <c r="E14" s="19" t="n">
+        <v>-401.202</v>
       </c>
       <c r="F14" s="17">
-        <f>-F13*Assumptions!$C$24</f>
+        <f>-F13*Assumptions!$C$48</f>
         <v/>
       </c>
       <c r="G14" s="17">
-        <f>-G13*Assumptions!$C$24</f>
+        <f>-G13*Assumptions!$C$48</f>
         <v/>
       </c>
       <c r="H14" s="17">
-        <f>-H13*Assumptions!$C$24</f>
+        <f>-H13*Assumptions!$C$48</f>
         <v/>
       </c>
       <c r="I14" s="17">
-        <f>-I13*Assumptions!$C$24</f>
+        <f>-I13*Assumptions!$C$48</f>
+        <v/>
+      </c>
+      <c r="J14" s="17">
+        <f>-J13*Assumptions!$C$48</f>
         <v/>
       </c>
     </row>
@@ -7731,9 +8444,8 @@
         <f>D13+D14</f>
         <v/>
       </c>
-      <c r="E15" s="17">
-        <f>E13+E14</f>
-        <v/>
+      <c r="E15" s="19" t="n">
+        <v>2202.138</v>
       </c>
       <c r="F15" s="17">
         <f>F13+F14</f>
@@ -7751,6 +8463,10 @@
         <f>I13+I14</f>
         <v/>
       </c>
+      <c r="J15" s="17">
+        <f>J13+J14</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -7767,24 +8483,27 @@
       <c r="D16" s="19" t="n">
         <v>-94.39699999999993</v>
       </c>
-      <c r="E16" s="17">
-        <f>E15*Assumptions!$C$25</f>
-        <v/>
+      <c r="E16" s="19" t="n">
+        <v>39.17200000000003</v>
       </c>
       <c r="F16" s="17">
-        <f>F15*Assumptions!$C$25</f>
+        <f>F15*Assumptions!$C$49</f>
         <v/>
       </c>
       <c r="G16" s="17">
-        <f>G15*Assumptions!$C$25</f>
+        <f>G15*Assumptions!$C$49</f>
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>H15*Assumptions!$C$25</f>
+        <f>H15*Assumptions!$C$49</f>
         <v/>
       </c>
       <c r="I16" s="17">
-        <f>I15*Assumptions!$C$25</f>
+        <f>I15*Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="J16" s="17">
+        <f>J15*Assumptions!$C$49</f>
         <v/>
       </c>
     </row>
@@ -7806,9 +8525,8 @@
         <f>D15-D16</f>
         <v/>
       </c>
-      <c r="E17" s="27">
-        <f>E15-E16</f>
-        <v/>
+      <c r="E17" s="33" t="n">
+        <v>2162.966</v>
       </c>
       <c r="F17" s="27">
         <f>F15-F16</f>
@@ -7824,6 +8542,10 @@
       </c>
       <c r="I17" s="27">
         <f>I15-I16</f>
+        <v/>
+      </c>
+      <c r="J17" s="27">
+        <f>J15-J16</f>
         <v/>
       </c>
     </row>
